--- a/IA_CCBS_BANK_SIDE/RepaymentSchedule/RepaymentSchedule_Simulation.xlsx
+++ b/IA_CCBS_BANK_SIDE/RepaymentSchedule/RepaymentSchedule_Simulation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Deploy\IA\InterfacesGitHub\IA_CCBS_BANK_SIDE\RepaymentSchedule\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sw\Relational_Files\iApply\Interfaces\Interfaces_plus_allbanks\IA_CCBS_BANK_SIDE\RepaymentSchedule\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D54D396F-765B-4C1F-8EC6-B9D4E2FC6129}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D1CA37B-19AD-4739-8BAE-7EF9AFD6C251}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15990" activeTab="1" xr2:uid="{CDB5EBE5-199B-4C02-A0AD-2F7510F763F7}"/>
+    <workbookView xWindow="28680" yWindow="-5550" windowWidth="30960" windowHeight="16920" xr2:uid="{CDB5EBE5-199B-4C02-A0AD-2F7510F763F7}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="3" r:id="rId1"/>
@@ -19,7 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Request!$C$2:$I$49</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Response!$C$2:$F$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Response!$C$2:$F$28</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="185">
   <si>
     <t>Description</t>
   </si>
@@ -514,9 +514,6 @@
   </si>
   <si>
     <t>Margin (+/-) on the Spread</t>
-  </si>
-  <si>
-    <t>Jul 28 2023, Dec 6 2024</t>
   </si>
   <si>
     <t>G4.24.12.6</t>
@@ -573,6 +570,26 @@
   </si>
   <si>
     <t>5/5/2025, Add</t>
+  </si>
+  <si>
+    <t>Jul 28 2023, Dec 6 2024, June 03 2025</t>
+  </si>
+  <si>
+    <t>The total costs of the loan in a single percentage</t>
+  </si>
+  <si>
+    <t>dae</t>
+  </si>
+  <si>
+    <t>cr_laresc_save</t>
+  </si>
+  <si>
+    <t>cr_laresc, 
+cr_laresc_insur_save</t>
+  </si>
+  <si>
+    <t>cr_laresc,
+cr_laresc_insur_save</t>
   </si>
 </sst>
 </file>
@@ -705,7 +722,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -728,41 +745,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -854,18 +843,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -893,26 +870,17 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1043,22 +1011,6 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -1072,22 +1024,6 @@
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -1101,22 +1037,6 @@
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -1130,22 +1050,6 @@
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -1159,22 +1063,6 @@
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -1188,22 +1076,6 @@
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1386,9 +1258,9 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{95AD6B62-2DA8-4727-83F6-7DF7747476EB}" name="Table4" displayName="Table4" ref="B2:H29" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
-  <autoFilter ref="B2:H29" xr:uid="{95AD6B62-2DA8-4727-83F6-7DF7747476EB}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:H29">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{95AD6B62-2DA8-4727-83F6-7DF7747476EB}" name="Table4" displayName="Table4" ref="B2:H28" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
+  <autoFilter ref="B2:H28" xr:uid="{95AD6B62-2DA8-4727-83F6-7DF7747476EB}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:H27">
     <sortCondition ref="B2"/>
   </sortState>
   <tableColumns count="7">
@@ -1702,20 +1574,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{687BD6CA-6839-469E-8EB3-DB0965AE2362}">
   <dimension ref="B2:C15"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="17"/>
-    <col min="2" max="2" width="12.44140625" style="17" customWidth="1"/>
-    <col min="3" max="3" width="66.6640625" style="17" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.109375" style="17"/>
+    <col min="1" max="1" width="9.140625" style="17"/>
+    <col min="2" max="2" width="12.42578125" style="17" customWidth="1"/>
+    <col min="3" max="3" width="66.7109375" style="17" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="17"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C2" s="20" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" s="20" t="s">
         <v>9</v>
       </c>
@@ -1723,7 +1595,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="20" t="s">
         <v>11</v>
       </c>
@@ -1731,37 +1603,37 @@
         <v>150</v>
       </c>
     </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" s="20" t="s">
         <v>17</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.3">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="20" t="s">
         <v>19</v>
       </c>
       <c r="C6" s="30" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.3">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B7" s="20"/>
       <c r="C7" s="21"/>
     </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" s="20" t="s">
         <v>15</v>
       </c>
       <c r="C8" s="21"/>
     </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B9" s="20"/>
       <c r="C9" s="21"/>
     </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" s="20" t="s">
         <v>12</v>
       </c>
@@ -1769,7 +1641,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B11" s="20" t="s">
         <v>14</v>
       </c>
@@ -1777,15 +1649,15 @@
         <v>151</v>
       </c>
     </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" s="20"/>
       <c r="C12" s="21"/>
     </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B13" s="20"/>
       <c r="C13" s="21"/>
     </row>
-    <row r="14" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B14" s="20" t="s">
         <v>18</v>
       </c>
@@ -1793,7 +1665,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="15" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B15" s="20"/>
       <c r="C15" s="21"/>
     </row>
@@ -1805,21 +1677,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA02E32A-0574-49FB-89B5-FAB0617EBB92}">
   <dimension ref="B1:I103"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.88671875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="9.109375" style="23"/>
+    <col min="1" max="1" width="2.85546875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="23"/>
     <col min="3" max="3" width="33" style="2" customWidth="1"/>
-    <col min="4" max="4" width="25.5546875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="22.6640625" style="2" customWidth="1"/>
-    <col min="6" max="7" width="28.5546875" style="2" customWidth="1"/>
-    <col min="8" max="8" width="16.33203125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="61.6640625" style="16" customWidth="1"/>
-    <col min="10" max="16384" width="9.109375" style="2"/>
+    <col min="4" max="4" width="25.5703125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" style="2" customWidth="1"/>
+    <col min="6" max="7" width="28.5703125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="16.28515625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="61.7109375" style="16" customWidth="1"/>
+    <col min="10" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:9" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:9" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:9" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="24" t="s">
         <v>16</v>
       </c>
@@ -1845,975 +1717,975 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B3" s="25">
         <v>1</v>
       </c>
-      <c r="C3" s="35" t="s">
+      <c r="C3" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="35"/>
-      <c r="E3" s="35" t="s">
+      <c r="D3" s="31"/>
+      <c r="E3" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="F3" s="36" t="s">
+      <c r="F3" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="36" t="s">
-        <v>154</v>
-      </c>
-      <c r="H3" s="42"/>
-      <c r="I3" s="35"/>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="G3" s="32" t="s">
+        <v>154</v>
+      </c>
+      <c r="H3" s="38"/>
+      <c r="I3" s="31"/>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B4" s="25">
         <v>2</v>
       </c>
-      <c r="C4" s="37" t="s">
+      <c r="C4" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="37"/>
-      <c r="E4" s="37" t="s">
+      <c r="D4" s="33"/>
+      <c r="E4" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="F4" s="35" t="s">
+      <c r="F4" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="36" t="s">
-        <v>154</v>
-      </c>
-      <c r="H4" s="42"/>
-      <c r="I4" s="37" t="s">
+      <c r="G4" s="32" t="s">
+        <v>154</v>
+      </c>
+      <c r="H4" s="38"/>
+      <c r="I4" s="33" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B5" s="25">
         <v>3</v>
       </c>
-      <c r="C5" s="37" t="s">
+      <c r="C5" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="37"/>
-      <c r="E5" s="37" t="s">
+      <c r="D5" s="33"/>
+      <c r="E5" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="F5" s="35" t="s">
+      <c r="F5" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="36" t="s">
-        <v>154</v>
-      </c>
-      <c r="H5" s="42"/>
-      <c r="I5" s="35"/>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="G5" s="32" t="s">
+        <v>154</v>
+      </c>
+      <c r="H5" s="38"/>
+      <c r="I5" s="31"/>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B6" s="25">
         <v>4</v>
       </c>
-      <c r="C6" s="37" t="s">
+      <c r="C6" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="37"/>
-      <c r="E6" s="37" t="s">
+      <c r="D6" s="33"/>
+      <c r="E6" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="F6" s="35" t="s">
+      <c r="F6" s="31" t="s">
         <v>57</v>
       </c>
-      <c r="G6" s="36" t="s">
-        <v>154</v>
-      </c>
-      <c r="H6" s="42"/>
-      <c r="I6" s="35"/>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="G6" s="32" t="s">
+        <v>154</v>
+      </c>
+      <c r="H6" s="38"/>
+      <c r="I6" s="31"/>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B7" s="25">
         <v>5</v>
       </c>
-      <c r="C7" s="37" t="s">
+      <c r="C7" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="37"/>
-      <c r="E7" s="37" t="s">
+      <c r="D7" s="33"/>
+      <c r="E7" s="33" t="s">
         <v>58</v>
       </c>
-      <c r="F7" s="35" t="s">
+      <c r="F7" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="G7" s="36" t="s">
-        <v>154</v>
-      </c>
-      <c r="H7" s="42"/>
-      <c r="I7" s="37"/>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="G7" s="32" t="s">
+        <v>154</v>
+      </c>
+      <c r="H7" s="38"/>
+      <c r="I7" s="33"/>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B8" s="25">
         <v>6</v>
       </c>
-      <c r="C8" s="37" t="s">
+      <c r="C8" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="37"/>
-      <c r="E8" s="37" t="s">
+      <c r="D8" s="33"/>
+      <c r="E8" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="F8" s="35" t="s">
+      <c r="F8" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="G8" s="36" t="s">
-        <v>154</v>
-      </c>
-      <c r="H8" s="42"/>
-      <c r="I8" s="37"/>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="G8" s="32" t="s">
+        <v>154</v>
+      </c>
+      <c r="H8" s="38"/>
+      <c r="I8" s="33"/>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B9" s="25">
         <v>7</v>
       </c>
-      <c r="C9" s="37" t="s">
+      <c r="C9" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="37"/>
-      <c r="E9" s="37" t="s">
+      <c r="D9" s="33"/>
+      <c r="E9" s="33" t="s">
         <v>59</v>
       </c>
-      <c r="F9" s="35" t="s">
+      <c r="F9" s="31" t="s">
         <v>60</v>
       </c>
-      <c r="G9" s="36" t="s">
-        <v>154</v>
-      </c>
-      <c r="H9" s="42"/>
-      <c r="I9" s="37"/>
-    </row>
-    <row r="10" spans="2:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="G9" s="32" t="s">
+        <v>154</v>
+      </c>
+      <c r="H9" s="38"/>
+      <c r="I9" s="33"/>
+    </row>
+    <row r="10" spans="2:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B10" s="25">
         <v>8</v>
       </c>
-      <c r="C10" s="35" t="s">
+      <c r="C10" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="35"/>
-      <c r="E10" s="37" t="s">
+      <c r="D10" s="31"/>
+      <c r="E10" s="33" t="s">
         <v>61</v>
       </c>
-      <c r="F10" s="35" t="s">
+      <c r="F10" s="31" t="s">
         <v>60</v>
       </c>
-      <c r="G10" s="36" t="s">
-        <v>154</v>
-      </c>
-      <c r="H10" s="42"/>
-      <c r="I10" s="37"/>
-    </row>
-    <row r="11" spans="2:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="G10" s="32" t="s">
+        <v>154</v>
+      </c>
+      <c r="H10" s="38"/>
+      <c r="I10" s="33"/>
+    </row>
+    <row r="11" spans="2:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B11" s="25">
         <v>9</v>
       </c>
-      <c r="C11" s="37" t="s">
+      <c r="C11" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="D11" s="37"/>
-      <c r="E11" s="37" t="s">
+      <c r="D11" s="33"/>
+      <c r="E11" s="33" t="s">
         <v>62</v>
       </c>
-      <c r="F11" s="35" t="s">
+      <c r="F11" s="31" t="s">
         <v>60</v>
       </c>
-      <c r="G11" s="36" t="s">
-        <v>154</v>
-      </c>
-      <c r="H11" s="42"/>
-      <c r="I11" s="37"/>
-    </row>
-    <row r="12" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="G11" s="32" t="s">
+        <v>154</v>
+      </c>
+      <c r="H11" s="38"/>
+      <c r="I11" s="33"/>
+    </row>
+    <row r="12" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B12" s="25">
         <v>10</v>
       </c>
-      <c r="C12" s="37" t="s">
+      <c r="C12" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="D12" s="37"/>
-      <c r="E12" s="37" t="s">
+      <c r="D12" s="33"/>
+      <c r="E12" s="33" t="s">
         <v>63</v>
       </c>
-      <c r="F12" s="35" t="s">
+      <c r="F12" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="G12" s="36" t="s">
-        <v>154</v>
-      </c>
-      <c r="H12" s="42"/>
-      <c r="I12" s="37"/>
-    </row>
-    <row r="13" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="G12" s="32" t="s">
+        <v>154</v>
+      </c>
+      <c r="H12" s="38"/>
+      <c r="I12" s="33"/>
+    </row>
+    <row r="13" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B13" s="25">
         <v>11</v>
       </c>
-      <c r="C13" s="35" t="s">
+      <c r="C13" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="35"/>
-      <c r="E13" s="37" t="s">
+      <c r="D13" s="31"/>
+      <c r="E13" s="33" t="s">
         <v>64</v>
       </c>
-      <c r="F13" s="35" t="s">
+      <c r="F13" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="G13" s="36" t="s">
-        <v>154</v>
-      </c>
-      <c r="H13" s="42"/>
-      <c r="I13" s="37"/>
-    </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="G13" s="32" t="s">
+        <v>154</v>
+      </c>
+      <c r="H13" s="38"/>
+      <c r="I13" s="33"/>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B14" s="25">
         <v>12</v>
       </c>
-      <c r="C14" s="37" t="s">
+      <c r="C14" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="D14" s="37"/>
-      <c r="E14" s="37" t="s">
+      <c r="D14" s="33"/>
+      <c r="E14" s="33" t="s">
         <v>65</v>
       </c>
-      <c r="F14" s="35" t="s">
+      <c r="F14" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="G14" s="36" t="s">
-        <v>154</v>
-      </c>
-      <c r="H14" s="42"/>
-      <c r="I14" s="37"/>
-    </row>
-    <row r="15" spans="2:9" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="G14" s="32" t="s">
+        <v>154</v>
+      </c>
+      <c r="H14" s="38"/>
+      <c r="I14" s="33"/>
+    </row>
+    <row r="15" spans="2:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B15" s="25">
         <v>13</v>
       </c>
-      <c r="C15" s="37" t="s">
+      <c r="C15" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="D15" s="37"/>
-      <c r="E15" s="37" t="s">
+      <c r="D15" s="33"/>
+      <c r="E15" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="F15" s="35" t="s">
+      <c r="F15" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="G15" s="36" t="s">
-        <v>154</v>
-      </c>
-      <c r="H15" s="42"/>
-      <c r="I15" s="37" t="s">
+      <c r="G15" s="32" t="s">
+        <v>154</v>
+      </c>
+      <c r="H15" s="38"/>
+      <c r="I15" s="33" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="16" spans="2:9" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B16" s="25">
         <v>14</v>
       </c>
-      <c r="C16" s="35" t="s">
+      <c r="C16" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="D16" s="35"/>
-      <c r="E16" s="37" t="s">
+      <c r="D16" s="31"/>
+      <c r="E16" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="F16" s="35" t="s">
+      <c r="F16" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="G16" s="36" t="s">
-        <v>154</v>
-      </c>
-      <c r="H16" s="42" t="s">
+      <c r="G16" s="32" t="s">
+        <v>154</v>
+      </c>
+      <c r="H16" s="38" t="s">
+        <v>163</v>
+      </c>
+      <c r="I16" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="I16" s="37" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B17" s="25">
         <v>15</v>
       </c>
-      <c r="C17" s="37" t="s">
+      <c r="C17" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="D17" s="37"/>
-      <c r="E17" s="37" t="s">
+      <c r="D17" s="33"/>
+      <c r="E17" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="F17" s="35" t="s">
+      <c r="F17" s="31" t="s">
         <v>70</v>
       </c>
-      <c r="G17" s="36" t="s">
-        <v>154</v>
-      </c>
-      <c r="H17" s="42"/>
-      <c r="I17" s="37"/>
-    </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="G17" s="32" t="s">
+        <v>154</v>
+      </c>
+      <c r="H17" s="38"/>
+      <c r="I17" s="33"/>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B18" s="25">
         <v>16</v>
       </c>
-      <c r="C18" s="37" t="s">
+      <c r="C18" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="D18" s="37"/>
-      <c r="E18" s="37" t="s">
+      <c r="D18" s="33"/>
+      <c r="E18" s="33" t="s">
         <v>71</v>
       </c>
-      <c r="F18" s="35" t="s">
+      <c r="F18" s="31" t="s">
         <v>70</v>
       </c>
-      <c r="G18" s="36" t="s">
-        <v>154</v>
-      </c>
-      <c r="H18" s="42"/>
-      <c r="I18" s="37"/>
-    </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="G18" s="32" t="s">
+        <v>154</v>
+      </c>
+      <c r="H18" s="38"/>
+      <c r="I18" s="33"/>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B19" s="25">
         <v>17</v>
       </c>
-      <c r="C19" s="37" t="s">
+      <c r="C19" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="D19" s="37"/>
-      <c r="E19" s="37" t="s">
+      <c r="D19" s="33"/>
+      <c r="E19" s="33" t="s">
         <v>72</v>
       </c>
-      <c r="F19" s="37" t="s">
+      <c r="F19" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="G19" s="36" t="s">
-        <v>154</v>
-      </c>
-      <c r="H19" s="42"/>
-      <c r="I19" s="37"/>
-    </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="G19" s="32" t="s">
+        <v>154</v>
+      </c>
+      <c r="H19" s="38"/>
+      <c r="I19" s="33"/>
+    </row>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B20" s="25">
         <v>18</v>
       </c>
-      <c r="C20" s="35" t="s">
+      <c r="C20" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="D20" s="35"/>
-      <c r="E20" s="37" t="s">
+      <c r="D20" s="31"/>
+      <c r="E20" s="33" t="s">
         <v>73</v>
       </c>
-      <c r="F20" s="37" t="s">
+      <c r="F20" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="G20" s="36" t="s">
-        <v>154</v>
-      </c>
-      <c r="H20" s="42"/>
-      <c r="I20" s="37"/>
-    </row>
-    <row r="21" spans="2:9" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="G20" s="32" t="s">
+        <v>154</v>
+      </c>
+      <c r="H20" s="38"/>
+      <c r="I20" s="33"/>
+    </row>
+    <row r="21" spans="2:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B21" s="25">
         <v>19</v>
       </c>
-      <c r="C21" s="37" t="s">
+      <c r="C21" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="D21" s="37"/>
-      <c r="E21" s="37" t="s">
+      <c r="D21" s="33"/>
+      <c r="E21" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="F21" s="37" t="s">
+      <c r="F21" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="G21" s="36" t="s">
-        <v>154</v>
-      </c>
-      <c r="H21" s="42" t="s">
-        <v>164</v>
-      </c>
-      <c r="I21" s="37" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="G21" s="32" t="s">
+        <v>154</v>
+      </c>
+      <c r="H21" s="38" t="s">
+        <v>163</v>
+      </c>
+      <c r="I21" s="33" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B22" s="25">
         <v>20</v>
       </c>
-      <c r="C22" s="35" t="s">
+      <c r="C22" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="D22" s="35"/>
-      <c r="E22" s="37" t="s">
+      <c r="D22" s="31"/>
+      <c r="E22" s="33" t="s">
         <v>75</v>
       </c>
-      <c r="F22" s="37" t="s">
+      <c r="F22" s="33" t="s">
         <v>60</v>
       </c>
-      <c r="G22" s="36" t="s">
-        <v>154</v>
-      </c>
-      <c r="H22" s="42"/>
-      <c r="I22" s="37"/>
-    </row>
-    <row r="23" spans="2:9" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="G22" s="32" t="s">
+        <v>154</v>
+      </c>
+      <c r="H22" s="38"/>
+      <c r="I22" s="33"/>
+    </row>
+    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B23" s="25">
         <v>21</v>
       </c>
-      <c r="C23" s="37" t="s">
+      <c r="C23" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="D23" s="37"/>
-      <c r="E23" s="37" t="s">
+      <c r="D23" s="33"/>
+      <c r="E23" s="33" t="s">
         <v>76</v>
       </c>
-      <c r="F23" s="37" t="s">
+      <c r="F23" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="G23" s="36" t="s">
-        <v>154</v>
-      </c>
-      <c r="H23" s="42"/>
-      <c r="I23" s="37" t="s">
+      <c r="G23" s="32" t="s">
+        <v>154</v>
+      </c>
+      <c r="H23" s="38"/>
+      <c r="I23" s="33" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B24" s="25">
         <v>22</v>
       </c>
-      <c r="C24" s="37" t="s">
+      <c r="C24" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="D24" s="37"/>
-      <c r="E24" s="37" t="s">
+      <c r="D24" s="33"/>
+      <c r="E24" s="33" t="s">
         <v>78</v>
       </c>
-      <c r="F24" s="37" t="s">
+      <c r="F24" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="G24" s="36" t="s">
-        <v>154</v>
-      </c>
-      <c r="H24" s="42"/>
-      <c r="I24" s="37"/>
-    </row>
-    <row r="25" spans="2:9" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="G24" s="32" t="s">
+        <v>154</v>
+      </c>
+      <c r="H24" s="38"/>
+      <c r="I24" s="33"/>
+    </row>
+    <row r="25" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B25" s="25">
         <v>23</v>
       </c>
-      <c r="C25" s="37" t="s">
+      <c r="C25" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="D25" s="37"/>
-      <c r="E25" s="37" t="s">
+      <c r="D25" s="33"/>
+      <c r="E25" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="F25" s="37" t="s">
+      <c r="F25" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="G25" s="36" t="s">
-        <v>154</v>
-      </c>
-      <c r="H25" s="42"/>
-      <c r="I25" s="37" t="s">
+      <c r="G25" s="32" t="s">
+        <v>154</v>
+      </c>
+      <c r="H25" s="38"/>
+      <c r="I25" s="33" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="26" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B26" s="25">
         <v>24</v>
       </c>
-      <c r="C26" s="35" t="s">
+      <c r="C26" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="D26" s="35"/>
-      <c r="E26" s="37" t="s">
+      <c r="D26" s="31"/>
+      <c r="E26" s="33" t="s">
         <v>80</v>
       </c>
-      <c r="F26" s="37" t="s">
+      <c r="F26" s="33" t="s">
         <v>60</v>
       </c>
-      <c r="G26" s="36" t="s">
-        <v>154</v>
-      </c>
-      <c r="H26" s="42"/>
-      <c r="I26" s="37"/>
-    </row>
-    <row r="27" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="G26" s="32" t="s">
+        <v>154</v>
+      </c>
+      <c r="H26" s="38"/>
+      <c r="I26" s="33"/>
+    </row>
+    <row r="27" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B27" s="25">
         <v>25</v>
       </c>
-      <c r="C27" s="37" t="s">
+      <c r="C27" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="D27" s="37"/>
-      <c r="E27" s="37" t="s">
+      <c r="D27" s="33"/>
+      <c r="E27" s="33" t="s">
         <v>81</v>
       </c>
-      <c r="F27" s="37" t="s">
+      <c r="F27" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="G27" s="36" t="s">
-        <v>154</v>
-      </c>
-      <c r="H27" s="42"/>
-      <c r="I27" s="37"/>
-    </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="G27" s="32" t="s">
+        <v>154</v>
+      </c>
+      <c r="H27" s="38"/>
+      <c r="I27" s="33"/>
+    </row>
+    <row r="28" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B28" s="25">
         <v>26</v>
       </c>
-      <c r="C28" s="37"/>
-      <c r="D28" s="37"/>
-      <c r="E28" s="37" t="s">
+      <c r="C28" s="33"/>
+      <c r="D28" s="33"/>
+      <c r="E28" s="33" t="s">
         <v>82</v>
       </c>
-      <c r="F28" s="37" t="s">
+      <c r="F28" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="G28" s="36" t="s">
-        <v>154</v>
-      </c>
-      <c r="H28" s="42"/>
-      <c r="I28" s="38">
+      <c r="G28" s="32" t="s">
+        <v>154</v>
+      </c>
+      <c r="H28" s="38"/>
+      <c r="I28" s="34">
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="2:9" s="3" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:9" s="3" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B29" s="25">
         <v>27</v>
       </c>
-      <c r="C29" s="37" t="s">
+      <c r="C29" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="D29" s="37"/>
-      <c r="E29" s="37" t="s">
+      <c r="D29" s="33"/>
+      <c r="E29" s="33" t="s">
         <v>83</v>
       </c>
-      <c r="F29" s="37" t="s">
+      <c r="F29" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="G29" s="36" t="s">
-        <v>154</v>
-      </c>
-      <c r="H29" s="42"/>
-      <c r="I29" s="37" t="s">
+      <c r="G29" s="32" t="s">
+        <v>154</v>
+      </c>
+      <c r="H29" s="38"/>
+      <c r="I29" s="33" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="30" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B30" s="25">
         <v>28</v>
       </c>
-      <c r="C30" s="37"/>
-      <c r="D30" s="37"/>
-      <c r="E30" s="37" t="s">
+      <c r="C30" s="33"/>
+      <c r="D30" s="33"/>
+      <c r="E30" s="33" t="s">
         <v>85</v>
       </c>
-      <c r="F30" s="37" t="s">
+      <c r="F30" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="G30" s="36" t="s">
-        <v>154</v>
-      </c>
-      <c r="H30" s="42"/>
-      <c r="I30" s="38">
+      <c r="G30" s="32" t="s">
+        <v>154</v>
+      </c>
+      <c r="H30" s="38"/>
+      <c r="I30" s="34">
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B31" s="25">
         <v>29</v>
       </c>
-      <c r="C31" s="37" t="s">
+      <c r="C31" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="D31" s="37"/>
-      <c r="E31" s="37" t="s">
+      <c r="D31" s="33"/>
+      <c r="E31" s="33" t="s">
         <v>86</v>
       </c>
-      <c r="F31" s="37" t="s">
+      <c r="F31" s="33" t="s">
         <v>60</v>
       </c>
-      <c r="G31" s="36" t="s">
-        <v>154</v>
-      </c>
-      <c r="H31" s="42"/>
-      <c r="I31" s="37"/>
-    </row>
-    <row r="32" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="G31" s="32" t="s">
+        <v>154</v>
+      </c>
+      <c r="H31" s="38"/>
+      <c r="I31" s="33"/>
+    </row>
+    <row r="32" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B32" s="25">
         <v>30</v>
       </c>
-      <c r="C32" s="37" t="s">
+      <c r="C32" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="D32" s="37"/>
-      <c r="E32" s="37" t="s">
+      <c r="D32" s="33"/>
+      <c r="E32" s="33" t="s">
         <v>87</v>
       </c>
-      <c r="F32" s="37" t="s">
+      <c r="F32" s="33" t="s">
         <v>60</v>
       </c>
-      <c r="G32" s="36" t="s">
-        <v>154</v>
-      </c>
-      <c r="H32" s="42"/>
-      <c r="I32" s="37"/>
-    </row>
-    <row r="33" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="G32" s="32" t="s">
+        <v>154</v>
+      </c>
+      <c r="H32" s="38"/>
+      <c r="I32" s="33"/>
+    </row>
+    <row r="33" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B33" s="25">
         <v>31</v>
       </c>
-      <c r="C33" s="37"/>
-      <c r="D33" s="37"/>
-      <c r="E33" s="37" t="s">
+      <c r="C33" s="33"/>
+      <c r="D33" s="33"/>
+      <c r="E33" s="33" t="s">
         <v>88</v>
       </c>
-      <c r="F33" s="37" t="s">
+      <c r="F33" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="G33" s="36" t="s">
-        <v>154</v>
-      </c>
-      <c r="H33" s="42"/>
-      <c r="I33" s="38">
+      <c r="G33" s="32" t="s">
+        <v>154</v>
+      </c>
+      <c r="H33" s="38"/>
+      <c r="I33" s="34">
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B34" s="25">
         <v>32</v>
       </c>
-      <c r="C34" s="37" t="s">
+      <c r="C34" s="33" t="s">
         <v>46</v>
       </c>
-      <c r="D34" s="37"/>
-      <c r="E34" s="37" t="s">
+      <c r="D34" s="33"/>
+      <c r="E34" s="33" t="s">
         <v>89</v>
       </c>
-      <c r="F34" s="37" t="s">
+      <c r="F34" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="G34" s="36" t="s">
-        <v>154</v>
-      </c>
-      <c r="H34" s="42"/>
-      <c r="I34" s="37"/>
-    </row>
-    <row r="35" spans="2:9" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="G34" s="32" t="s">
+        <v>154</v>
+      </c>
+      <c r="H34" s="38"/>
+      <c r="I34" s="33"/>
+    </row>
+    <row r="35" spans="2:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B35" s="25">
         <v>33</v>
       </c>
-      <c r="C35" s="37"/>
-      <c r="D35" s="37"/>
-      <c r="E35" s="37" t="s">
+      <c r="C35" s="33"/>
+      <c r="D35" s="33"/>
+      <c r="E35" s="33" t="s">
         <v>90</v>
       </c>
-      <c r="F35" s="37" t="s">
+      <c r="F35" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="G35" s="36" t="s">
-        <v>154</v>
-      </c>
-      <c r="H35" s="42"/>
-      <c r="I35" s="37" t="s">
+      <c r="G35" s="32" t="s">
+        <v>154</v>
+      </c>
+      <c r="H35" s="38"/>
+      <c r="I35" s="33" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="36" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B36" s="25">
         <v>34</v>
       </c>
-      <c r="C36" s="37" t="s">
+      <c r="C36" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="D36" s="37"/>
-      <c r="E36" s="37" t="s">
+      <c r="D36" s="33"/>
+      <c r="E36" s="33" t="s">
         <v>92</v>
       </c>
-      <c r="F36" s="37" t="s">
+      <c r="F36" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="G36" s="36" t="s">
-        <v>154</v>
-      </c>
-      <c r="H36" s="42"/>
-      <c r="I36" s="37"/>
-    </row>
-    <row r="37" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="G36" s="32" t="s">
+        <v>154</v>
+      </c>
+      <c r="H36" s="38"/>
+      <c r="I36" s="33"/>
+    </row>
+    <row r="37" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B37" s="25">
         <v>35</v>
       </c>
-      <c r="C37" s="37" t="s">
+      <c r="C37" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="D37" s="37"/>
-      <c r="E37" s="37" t="s">
+      <c r="D37" s="33"/>
+      <c r="E37" s="33" t="s">
         <v>93</v>
       </c>
-      <c r="F37" s="37" t="s">
+      <c r="F37" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="G37" s="36" t="s">
-        <v>154</v>
-      </c>
-      <c r="H37" s="42"/>
-      <c r="I37" s="37"/>
-    </row>
-    <row r="38" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="G37" s="32" t="s">
+        <v>154</v>
+      </c>
+      <c r="H37" s="38"/>
+      <c r="I37" s="33"/>
+    </row>
+    <row r="38" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B38" s="25">
         <v>36</v>
       </c>
-      <c r="C38" s="37"/>
-      <c r="D38" s="37"/>
-      <c r="E38" s="37" t="s">
+      <c r="C38" s="33"/>
+      <c r="D38" s="33"/>
+      <c r="E38" s="33" t="s">
         <v>94</v>
       </c>
-      <c r="F38" s="37" t="s">
+      <c r="F38" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="G38" s="36" t="s">
-        <v>154</v>
-      </c>
-      <c r="H38" s="42"/>
-      <c r="I38" s="38">
+      <c r="G38" s="32" t="s">
+        <v>154</v>
+      </c>
+      <c r="H38" s="38"/>
+      <c r="I38" s="34">
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B39" s="25">
         <v>37</v>
       </c>
-      <c r="C39" s="37"/>
-      <c r="D39" s="37"/>
-      <c r="E39" s="37" t="s">
+      <c r="C39" s="33"/>
+      <c r="D39" s="33"/>
+      <c r="E39" s="33" t="s">
         <v>95</v>
       </c>
-      <c r="F39" s="37" t="s">
+      <c r="F39" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="G39" s="36" t="s">
-        <v>154</v>
-      </c>
-      <c r="H39" s="42"/>
-      <c r="I39" s="38">
+      <c r="G39" s="32" t="s">
+        <v>154</v>
+      </c>
+      <c r="H39" s="38"/>
+      <c r="I39" s="34">
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B40" s="25">
         <v>38</v>
       </c>
-      <c r="C40" s="37"/>
-      <c r="D40" s="37"/>
-      <c r="E40" s="37" t="s">
+      <c r="C40" s="33"/>
+      <c r="D40" s="33"/>
+      <c r="E40" s="33" t="s">
         <v>96</v>
       </c>
-      <c r="F40" s="37" t="s">
+      <c r="F40" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="G40" s="36" t="s">
-        <v>154</v>
-      </c>
-      <c r="H40" s="42"/>
-      <c r="I40" s="38">
+      <c r="G40" s="32" t="s">
+        <v>154</v>
+      </c>
+      <c r="H40" s="38"/>
+      <c r="I40" s="34">
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B41" s="25">
         <v>39</v>
       </c>
-      <c r="C41" s="37"/>
-      <c r="D41" s="37"/>
-      <c r="E41" s="37" t="s">
+      <c r="C41" s="33"/>
+      <c r="D41" s="33"/>
+      <c r="E41" s="33" t="s">
         <v>97</v>
       </c>
-      <c r="F41" s="37" t="s">
+      <c r="F41" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="G41" s="36" t="s">
-        <v>154</v>
-      </c>
-      <c r="H41" s="42"/>
-      <c r="I41" s="38">
+      <c r="G41" s="32" t="s">
+        <v>154</v>
+      </c>
+      <c r="H41" s="38"/>
+      <c r="I41" s="34">
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B42" s="25">
         <v>40</v>
       </c>
-      <c r="C42" s="37" t="s">
+      <c r="C42" s="33" t="s">
         <v>49</v>
       </c>
-      <c r="D42" s="37"/>
-      <c r="E42" s="37" t="s">
+      <c r="D42" s="33"/>
+      <c r="E42" s="33" t="s">
         <v>98</v>
       </c>
-      <c r="F42" s="37" t="s">
+      <c r="F42" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="G42" s="36" t="s">
-        <v>154</v>
-      </c>
-      <c r="H42" s="42"/>
-      <c r="I42" s="37" t="s">
+      <c r="G42" s="32" t="s">
+        <v>154</v>
+      </c>
+      <c r="H42" s="38"/>
+      <c r="I42" s="33" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="43" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B43" s="25">
         <v>41</v>
       </c>
-      <c r="C43" s="37" t="s">
+      <c r="C43" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="D43" s="37"/>
-      <c r="E43" s="37" t="s">
+      <c r="D43" s="33"/>
+      <c r="E43" s="33" t="s">
         <v>100</v>
       </c>
-      <c r="F43" s="37" t="s">
+      <c r="F43" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="G43" s="36" t="s">
-        <v>154</v>
-      </c>
-      <c r="H43" s="42"/>
-      <c r="I43" s="37"/>
-    </row>
-    <row r="44" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="G43" s="32" t="s">
+        <v>154</v>
+      </c>
+      <c r="H43" s="38"/>
+      <c r="I43" s="33"/>
+    </row>
+    <row r="44" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B44" s="25">
         <v>42</v>
       </c>
-      <c r="C44" s="37" t="s">
+      <c r="C44" s="33" t="s">
         <v>51</v>
       </c>
-      <c r="D44" s="37"/>
-      <c r="E44" s="37" t="s">
+      <c r="D44" s="33"/>
+      <c r="E44" s="33" t="s">
         <v>101</v>
       </c>
-      <c r="F44" s="37" t="s">
+      <c r="F44" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="G44" s="36" t="s">
-        <v>154</v>
-      </c>
-      <c r="H44" s="42"/>
-      <c r="I44" s="37"/>
-    </row>
-    <row r="45" spans="2:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="G44" s="32" t="s">
+        <v>154</v>
+      </c>
+      <c r="H44" s="38"/>
+      <c r="I44" s="33"/>
+    </row>
+    <row r="45" spans="2:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B45" s="25">
         <v>43</v>
       </c>
-      <c r="C45" s="40" t="s">
+      <c r="C45" s="36" t="s">
         <v>160</v>
       </c>
-      <c r="D45" s="39"/>
-      <c r="E45" s="40" t="s">
+      <c r="D45" s="35"/>
+      <c r="E45" s="36" t="s">
         <v>159</v>
       </c>
-      <c r="F45" s="41" t="s">
+      <c r="F45" s="37" t="s">
         <v>158</v>
       </c>
-      <c r="G45" s="37"/>
-      <c r="H45" s="43" t="s">
-        <v>163</v>
-      </c>
-      <c r="I45" s="39"/>
-    </row>
-    <row r="46" spans="2:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B46" s="49">
+      <c r="G45" s="33"/>
+      <c r="H45" s="39" t="s">
+        <v>162</v>
+      </c>
+      <c r="I45" s="35"/>
+    </row>
+    <row r="46" spans="2:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="25">
         <v>44</v>
       </c>
-      <c r="C46" s="44" t="s">
+      <c r="C46" s="36" t="s">
+        <v>172</v>
+      </c>
+      <c r="D46" s="35"/>
+      <c r="E46" s="36" t="s">
         <v>173</v>
       </c>
-      <c r="D46" s="45"/>
-      <c r="E46" s="44" t="s">
+      <c r="F46" s="37" t="s">
+        <v>169</v>
+      </c>
+      <c r="G46" s="33"/>
+      <c r="H46" s="40" t="s">
+        <v>178</v>
+      </c>
+      <c r="I46" s="33" t="s">
         <v>174</v>
       </c>
-      <c r="F46" s="46" t="s">
-        <v>170</v>
-      </c>
-      <c r="G46" s="47"/>
-      <c r="H46" s="48" t="s">
-        <v>179</v>
-      </c>
-      <c r="I46" s="47" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="47" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="47" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B47" s="25">
         <v>45</v>
       </c>
-      <c r="C47" s="47" t="s">
-        <v>167</v>
-      </c>
-      <c r="D47" s="47"/>
-      <c r="E47" s="47" t="s">
+      <c r="C47" s="33" t="s">
+        <v>166</v>
+      </c>
+      <c r="D47" s="33"/>
+      <c r="E47" s="33" t="s">
         <v>107</v>
       </c>
-      <c r="F47" s="50" t="s">
-        <v>170</v>
-      </c>
-      <c r="G47" s="47"/>
-      <c r="H47" s="48" t="s">
-        <v>179</v>
-      </c>
-      <c r="I47" s="47" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="48" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="F47" s="31" t="s">
+        <v>169</v>
+      </c>
+      <c r="G47" s="33"/>
+      <c r="H47" s="40" t="s">
+        <v>178</v>
+      </c>
+      <c r="I47" s="33" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="48" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B48" s="25">
         <v>46</v>
       </c>
-      <c r="C48" s="47" t="s">
+      <c r="C48" s="33" t="s">
+        <v>176</v>
+      </c>
+      <c r="D48" s="33"/>
+      <c r="E48" s="33" t="s">
         <v>177</v>
       </c>
-      <c r="D48" s="47"/>
-      <c r="E48" s="47" t="s">
+      <c r="F48" s="31" t="s">
+        <v>169</v>
+      </c>
+      <c r="G48" s="33"/>
+      <c r="H48" s="40" t="s">
         <v>178</v>
       </c>
-      <c r="F48" s="50" t="s">
+      <c r="I48" s="33" t="s">
         <v>170</v>
       </c>
-      <c r="G48" s="47"/>
-      <c r="H48" s="48" t="s">
-        <v>179</v>
-      </c>
-      <c r="I48" s="47" t="s">
+    </row>
+    <row r="49" spans="2:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="25">
+        <v>47</v>
+      </c>
+      <c r="C49" s="36" t="s">
+        <v>167</v>
+      </c>
+      <c r="D49" s="35"/>
+      <c r="E49" s="36" t="s">
+        <v>168</v>
+      </c>
+      <c r="F49" s="37" t="s">
+        <v>158</v>
+      </c>
+      <c r="G49" s="33"/>
+      <c r="H49" s="40" t="s">
+        <v>178</v>
+      </c>
+      <c r="I49" s="33" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="49" spans="2:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B49" s="49">
-        <v>47</v>
-      </c>
-      <c r="C49" s="44" t="s">
-        <v>168</v>
-      </c>
-      <c r="D49" s="45"/>
-      <c r="E49" s="44" t="s">
-        <v>169</v>
-      </c>
-      <c r="F49" s="46" t="s">
-        <v>158</v>
-      </c>
-      <c r="G49" s="47"/>
-      <c r="H49" s="48" t="s">
-        <v>179</v>
-      </c>
-      <c r="I49" s="47" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="50" spans="2:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B50" s="26"/>
       <c r="C50" s="7"/>
       <c r="D50" s="22"/>
@@ -2823,7 +2695,7 @@
       <c r="H50" s="8"/>
       <c r="I50" s="7"/>
     </row>
-    <row r="51" spans="2:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B51" s="26"/>
       <c r="C51" s="7"/>
       <c r="D51" s="22"/>
@@ -2833,7 +2705,7 @@
       <c r="H51" s="8"/>
       <c r="I51" s="7"/>
     </row>
-    <row r="52" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C52" s="9"/>
       <c r="D52" s="9"/>
       <c r="E52" s="9"/>
@@ -2842,7 +2714,7 @@
       <c r="H52" s="10"/>
       <c r="I52" s="9"/>
     </row>
-    <row r="53" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C53" s="5"/>
       <c r="D53" s="5"/>
       <c r="E53" s="5"/>
@@ -2851,7 +2723,7 @@
       <c r="H53" s="6"/>
       <c r="I53" s="5"/>
     </row>
-    <row r="54" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B54" s="27"/>
       <c r="C54" s="5"/>
       <c r="D54" s="5"/>
@@ -2861,7 +2733,7 @@
       <c r="H54" s="6"/>
       <c r="I54" s="5"/>
     </row>
-    <row r="55" spans="2:9" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:9" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B55" s="28"/>
       <c r="C55" s="9"/>
       <c r="D55" s="9"/>
@@ -2871,7 +2743,7 @@
       <c r="H55" s="10"/>
       <c r="I55" s="9"/>
     </row>
-    <row r="56" spans="2:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B56" s="26"/>
       <c r="C56" s="9"/>
       <c r="D56" s="9"/>
@@ -2881,7 +2753,7 @@
       <c r="H56" s="10"/>
       <c r="I56" s="9"/>
     </row>
-    <row r="57" spans="2:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B57" s="26"/>
       <c r="C57" s="9"/>
       <c r="D57" s="9"/>
@@ -2891,7 +2763,7 @@
       <c r="H57" s="10"/>
       <c r="I57" s="9"/>
     </row>
-    <row r="58" spans="2:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B58" s="26"/>
       <c r="C58" s="9"/>
       <c r="D58" s="9"/>
@@ -2901,7 +2773,7 @@
       <c r="H58" s="10"/>
       <c r="I58" s="9"/>
     </row>
-    <row r="59" spans="2:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B59" s="26"/>
       <c r="C59" s="12"/>
       <c r="D59" s="12"/>
@@ -2911,7 +2783,7 @@
       <c r="H59" s="13"/>
       <c r="I59" s="12"/>
     </row>
-    <row r="60" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C60" s="5"/>
       <c r="D60" s="5"/>
       <c r="E60" s="5"/>
@@ -2920,7 +2792,7 @@
       <c r="H60" s="6"/>
       <c r="I60" s="5"/>
     </row>
-    <row r="61" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C61" s="5"/>
       <c r="D61" s="5"/>
       <c r="E61" s="5"/>
@@ -2929,7 +2801,7 @@
       <c r="H61" s="6"/>
       <c r="I61" s="5"/>
     </row>
-    <row r="62" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C62" s="5"/>
       <c r="D62" s="5"/>
       <c r="E62" s="5"/>
@@ -2938,7 +2810,7 @@
       <c r="H62" s="6"/>
       <c r="I62" s="5"/>
     </row>
-    <row r="63" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C63" s="5"/>
       <c r="D63" s="5"/>
       <c r="E63" s="5"/>
@@ -2947,7 +2819,7 @@
       <c r="H63" s="6"/>
       <c r="I63" s="5"/>
     </row>
-    <row r="64" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B64" s="27"/>
       <c r="C64" s="5"/>
       <c r="D64" s="5"/>
@@ -2957,7 +2829,7 @@
       <c r="H64" s="6"/>
       <c r="I64" s="5"/>
     </row>
-    <row r="65" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B65" s="27"/>
       <c r="C65" s="9"/>
       <c r="D65" s="9"/>
@@ -2967,7 +2839,7 @@
       <c r="H65" s="10"/>
       <c r="I65" s="9"/>
     </row>
-    <row r="66" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B66" s="27"/>
       <c r="C66" s="9"/>
       <c r="D66" s="9"/>
@@ -2977,7 +2849,7 @@
       <c r="H66" s="10"/>
       <c r="I66" s="9"/>
     </row>
-    <row r="67" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C67" s="5"/>
       <c r="D67" s="5"/>
       <c r="E67" s="5"/>
@@ -2986,7 +2858,7 @@
       <c r="H67" s="6"/>
       <c r="I67" s="5"/>
     </row>
-    <row r="68" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C68" s="5"/>
       <c r="D68" s="5"/>
       <c r="E68" s="5"/>
@@ -2995,7 +2867,7 @@
       <c r="H68" s="6"/>
       <c r="I68" s="5"/>
     </row>
-    <row r="69" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C69" s="9"/>
       <c r="D69" s="9"/>
       <c r="E69" s="9"/>
@@ -3004,7 +2876,7 @@
       <c r="H69" s="10"/>
       <c r="I69" s="9"/>
     </row>
-    <row r="70" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C70" s="5"/>
       <c r="D70" s="5"/>
       <c r="E70" s="5"/>
@@ -3013,7 +2885,7 @@
       <c r="H70" s="6"/>
       <c r="I70" s="5"/>
     </row>
-    <row r="71" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C71" s="5"/>
       <c r="D71" s="5"/>
       <c r="E71" s="5"/>
@@ -3022,7 +2894,7 @@
       <c r="H71" s="6"/>
       <c r="I71" s="14"/>
     </row>
-    <row r="72" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C72" s="5"/>
       <c r="D72" s="5"/>
       <c r="E72" s="5"/>
@@ -3031,7 +2903,7 @@
       <c r="H72" s="6"/>
       <c r="I72" s="14"/>
     </row>
-    <row r="73" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C73" s="5"/>
       <c r="D73" s="5"/>
       <c r="E73" s="5"/>
@@ -3040,7 +2912,7 @@
       <c r="H73" s="6"/>
       <c r="I73" s="14"/>
     </row>
-    <row r="74" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B74" s="27"/>
       <c r="C74" s="5"/>
       <c r="D74" s="5"/>
@@ -3050,7 +2922,7 @@
       <c r="H74" s="6"/>
       <c r="I74" s="5"/>
     </row>
-    <row r="75" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B75" s="27"/>
       <c r="C75" s="5"/>
       <c r="D75" s="5"/>
@@ -3060,7 +2932,7 @@
       <c r="H75" s="6"/>
       <c r="I75" s="5"/>
     </row>
-    <row r="76" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B76" s="27"/>
       <c r="C76" s="5"/>
       <c r="D76" s="5"/>
@@ -3070,7 +2942,7 @@
       <c r="H76" s="6"/>
       <c r="I76" s="5"/>
     </row>
-    <row r="77" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C77" s="5"/>
       <c r="D77" s="5"/>
       <c r="E77" s="5"/>
@@ -3079,7 +2951,7 @@
       <c r="H77" s="6"/>
       <c r="I77" s="5"/>
     </row>
-    <row r="78" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C78" s="5"/>
       <c r="D78" s="5"/>
       <c r="E78" s="5"/>
@@ -3088,7 +2960,7 @@
       <c r="H78" s="6"/>
       <c r="I78" s="5"/>
     </row>
-    <row r="79" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C79" s="5"/>
       <c r="D79" s="5"/>
       <c r="E79" s="5"/>
@@ -3097,7 +2969,7 @@
       <c r="H79" s="6"/>
       <c r="I79" s="5"/>
     </row>
-    <row r="80" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C80" s="5"/>
       <c r="D80" s="5"/>
       <c r="E80" s="5"/>
@@ -3106,7 +2978,7 @@
       <c r="H80" s="6"/>
       <c r="I80" s="5"/>
     </row>
-    <row r="81" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="81" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C81" s="5"/>
       <c r="D81" s="5"/>
       <c r="E81" s="5"/>
@@ -3115,7 +2987,7 @@
       <c r="H81" s="6"/>
       <c r="I81" s="5"/>
     </row>
-    <row r="82" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="82" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C82" s="5"/>
       <c r="D82" s="5"/>
       <c r="E82" s="5"/>
@@ -3124,7 +2996,7 @@
       <c r="H82" s="6"/>
       <c r="I82" s="5"/>
     </row>
-    <row r="83" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="83" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C83" s="5"/>
       <c r="D83" s="5"/>
       <c r="E83" s="5"/>
@@ -3133,7 +3005,7 @@
       <c r="H83" s="6"/>
       <c r="I83" s="5"/>
     </row>
-    <row r="84" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="84" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C84" s="5"/>
       <c r="D84" s="5"/>
       <c r="E84" s="5"/>
@@ -3142,7 +3014,7 @@
       <c r="H84" s="6"/>
       <c r="I84" s="5"/>
     </row>
-    <row r="85" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="85" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C85" s="5"/>
       <c r="D85" s="5"/>
       <c r="E85" s="5"/>
@@ -3151,7 +3023,7 @@
       <c r="H85" s="6"/>
       <c r="I85" s="5"/>
     </row>
-    <row r="86" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="86" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C86" s="5"/>
       <c r="D86" s="5"/>
       <c r="E86" s="5"/>
@@ -3160,7 +3032,7 @@
       <c r="H86" s="6"/>
       <c r="I86" s="5"/>
     </row>
-    <row r="87" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="87" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C87" s="5"/>
       <c r="D87" s="5"/>
       <c r="E87" s="5"/>
@@ -3169,7 +3041,7 @@
       <c r="H87" s="6"/>
       <c r="I87" s="5"/>
     </row>
-    <row r="88" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="88" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C88" s="5"/>
       <c r="D88" s="5"/>
       <c r="E88" s="5"/>
@@ -3178,7 +3050,7 @@
       <c r="H88" s="6"/>
       <c r="I88" s="5"/>
     </row>
-    <row r="89" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="89" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C89" s="5"/>
       <c r="D89" s="5"/>
       <c r="E89" s="5"/>
@@ -3187,7 +3059,7 @@
       <c r="H89" s="6"/>
       <c r="I89" s="7"/>
     </row>
-    <row r="90" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="90" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C90" s="5"/>
       <c r="D90" s="5"/>
       <c r="E90" s="5"/>
@@ -3196,7 +3068,7 @@
       <c r="H90" s="6"/>
       <c r="I90" s="7"/>
     </row>
-    <row r="91" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="91" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C91" s="5"/>
       <c r="D91" s="5"/>
       <c r="E91" s="5"/>
@@ -3205,7 +3077,7 @@
       <c r="H91" s="6"/>
       <c r="I91" s="7"/>
     </row>
-    <row r="92" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="92" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C92" s="5"/>
       <c r="D92" s="5"/>
       <c r="E92" s="5"/>
@@ -3214,7 +3086,7 @@
       <c r="H92" s="6"/>
       <c r="I92" s="5"/>
     </row>
-    <row r="93" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="93" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C93" s="5"/>
       <c r="D93" s="5"/>
       <c r="E93" s="5"/>
@@ -3223,7 +3095,7 @@
       <c r="H93" s="6"/>
       <c r="I93" s="5"/>
     </row>
-    <row r="94" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="94" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C94" s="5"/>
       <c r="D94" s="5"/>
       <c r="E94" s="5"/>
@@ -3232,7 +3104,7 @@
       <c r="H94" s="6"/>
       <c r="I94" s="5"/>
     </row>
-    <row r="95" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="95" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C95" s="5"/>
       <c r="D95" s="5"/>
       <c r="E95" s="5"/>
@@ -3241,7 +3113,7 @@
       <c r="H95" s="6"/>
       <c r="I95" s="5"/>
     </row>
-    <row r="96" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="96" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C96" s="5"/>
       <c r="D96" s="5"/>
       <c r="E96" s="5"/>
@@ -3250,7 +3122,7 @@
       <c r="H96" s="6"/>
       <c r="I96" s="5"/>
     </row>
-    <row r="97" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B97" s="27"/>
       <c r="C97" s="9"/>
       <c r="D97" s="9"/>
@@ -3260,7 +3132,7 @@
       <c r="H97" s="10"/>
       <c r="I97" s="9"/>
     </row>
-    <row r="98" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B98" s="27"/>
       <c r="C98" s="5"/>
       <c r="D98" s="5"/>
@@ -3270,7 +3142,7 @@
       <c r="H98" s="6"/>
       <c r="I98" s="5"/>
     </row>
-    <row r="99" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B99" s="27"/>
       <c r="C99" s="5"/>
       <c r="D99" s="5"/>
@@ -3280,7 +3152,7 @@
       <c r="H99" s="6"/>
       <c r="I99" s="5"/>
     </row>
-    <row r="100" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C100" s="5"/>
       <c r="D100" s="5"/>
       <c r="E100" s="5"/>
@@ -3289,7 +3161,7 @@
       <c r="H100" s="6"/>
       <c r="I100" s="5"/>
     </row>
-    <row r="101" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C101" s="5"/>
       <c r="D101" s="5"/>
       <c r="E101" s="5"/>
@@ -3298,7 +3170,7 @@
       <c r="H101" s="6"/>
       <c r="I101" s="5"/>
     </row>
-    <row r="102" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B102" s="29"/>
       <c r="C102" s="5"/>
       <c r="D102" s="5"/>
@@ -3308,7 +3180,7 @@
       <c r="H102" s="6"/>
       <c r="I102" s="5"/>
     </row>
-    <row r="103" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C103" s="5"/>
       <c r="D103" s="5"/>
       <c r="E103" s="5"/>
@@ -3341,18 +3213,18 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF72A13E-C145-44E7-92A5-8C7F37AE7802}">
-  <dimension ref="B2:H29"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="B2:H28"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="9.109375" style="17"/>
-    <col min="3" max="3" width="33.33203125" customWidth="1"/>
-    <col min="4" max="4" width="32.5546875" customWidth="1"/>
-    <col min="5" max="6" width="33.33203125" customWidth="1"/>
-    <col min="7" max="7" width="28.5546875" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="17"/>
+    <col min="3" max="3" width="39.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="32.5703125" customWidth="1"/>
+    <col min="5" max="6" width="33.28515625" customWidth="1"/>
+    <col min="7" max="7" width="28.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:8" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="18" t="s">
         <v>16</v>
       </c>
@@ -3375,524 +3247,505 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:8" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B3" s="18">
         <v>1</v>
       </c>
-      <c r="C3" s="31" t="s">
+      <c r="C3" s="41" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31" t="s">
+      <c r="D3" s="41"/>
+      <c r="E3" s="41" t="s">
         <v>103</v>
       </c>
-      <c r="F3" s="31" t="s">
+      <c r="F3" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="31" t="s">
-        <v>155</v>
-      </c>
-      <c r="H3" s="34"/>
-    </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="G3" s="43" t="s">
+        <v>183</v>
+      </c>
+      <c r="H3" s="42"/>
+    </row>
+    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B4" s="18">
         <v>2</v>
       </c>
-      <c r="C4" s="31" t="s">
+      <c r="C4" s="41" t="s">
         <v>104</v>
       </c>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31" t="s">
+      <c r="D4" s="41"/>
+      <c r="E4" s="41" t="s">
         <v>105</v>
       </c>
-      <c r="F4" s="31" t="s">
+      <c r="F4" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="31" t="s">
+      <c r="G4" s="41" t="s">
         <v>155</v>
       </c>
-      <c r="H4" s="33"/>
-    </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H4" s="42"/>
+    </row>
+    <row r="5" spans="2:8" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B5" s="18">
         <v>3</v>
       </c>
-      <c r="C5" s="31" t="s">
+      <c r="C5" s="41" t="s">
         <v>106</v>
       </c>
-      <c r="D5" s="31"/>
-      <c r="E5" s="31" t="s">
+      <c r="D5" s="41"/>
+      <c r="E5" s="41" t="s">
         <v>107</v>
       </c>
-      <c r="F5" s="31" t="s">
+      <c r="F5" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="31" t="s">
-        <v>155</v>
-      </c>
-      <c r="H5" s="33">
+      <c r="G5" s="43" t="s">
+        <v>184</v>
+      </c>
+      <c r="H5" s="42">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="18">
         <v>4</v>
       </c>
-      <c r="C6" s="31" t="s">
+      <c r="C6" s="41" t="s">
         <v>108</v>
       </c>
-      <c r="D6" s="31"/>
-      <c r="E6" s="31" t="s">
+      <c r="D6" s="41"/>
+      <c r="E6" s="41" t="s">
         <v>109</v>
       </c>
-      <c r="F6" s="31" t="s">
+      <c r="F6" s="41" t="s">
         <v>110</v>
       </c>
-      <c r="G6" s="31" t="s">
+      <c r="G6" s="41" t="s">
         <v>155</v>
       </c>
-      <c r="H6" s="33"/>
-    </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H6" s="42"/>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B7" s="18">
         <v>5</v>
       </c>
-      <c r="C7" s="31" t="s">
+      <c r="C7" s="41" t="s">
         <v>111</v>
       </c>
-      <c r="D7" s="31"/>
-      <c r="E7" s="31" t="s">
+      <c r="D7" s="41"/>
+      <c r="E7" s="41" t="s">
         <v>112</v>
       </c>
-      <c r="F7" s="31" t="s">
+      <c r="F7" s="41" t="s">
         <v>110</v>
       </c>
-      <c r="G7" s="31" t="s">
+      <c r="G7" s="41" t="s">
         <v>155</v>
       </c>
-      <c r="H7" s="33"/>
-    </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H7" s="42"/>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B8" s="18">
         <v>6</v>
       </c>
-      <c r="C8" s="31" t="s">
+      <c r="C8" s="41" t="s">
         <v>113</v>
       </c>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31" t="s">
+      <c r="D8" s="41"/>
+      <c r="E8" s="41" t="s">
         <v>114</v>
       </c>
-      <c r="F8" s="31" t="s">
+      <c r="F8" s="41" t="s">
         <v>110</v>
       </c>
-      <c r="G8" s="31" t="s">
+      <c r="G8" s="41" t="s">
         <v>155</v>
       </c>
-      <c r="H8" s="33"/>
-    </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H8" s="42"/>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B9" s="18">
         <v>7</v>
       </c>
-      <c r="C9" s="31" t="s">
+      <c r="C9" s="41" t="s">
         <v>115</v>
       </c>
-      <c r="D9" s="31"/>
-      <c r="E9" s="32" t="s">
+      <c r="D9" s="41"/>
+      <c r="E9" s="43" t="s">
         <v>116</v>
       </c>
-      <c r="F9" s="31" t="s">
+      <c r="F9" s="41" t="s">
         <v>110</v>
       </c>
-      <c r="G9" s="31" t="s">
+      <c r="G9" s="41" t="s">
         <v>155</v>
       </c>
-      <c r="H9" s="33"/>
-    </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H9" s="42"/>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B10" s="18">
         <v>8</v>
       </c>
-      <c r="C10" s="31" t="s">
+      <c r="C10" s="41" t="s">
         <v>117</v>
       </c>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31" t="s">
+      <c r="D10" s="41"/>
+      <c r="E10" s="41" t="s">
         <v>118</v>
       </c>
-      <c r="F10" s="31" t="s">
+      <c r="F10" s="41" t="s">
         <v>110</v>
       </c>
-      <c r="G10" s="31" t="s">
+      <c r="G10" s="41" t="s">
         <v>155</v>
       </c>
-      <c r="H10" s="33"/>
-    </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H10" s="42"/>
+    </row>
+    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B11" s="18">
         <v>9</v>
       </c>
-      <c r="C11" s="31" t="s">
+      <c r="C11" s="41" t="s">
         <v>74</v>
       </c>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31" t="s">
+      <c r="D11" s="41"/>
+      <c r="E11" s="41" t="s">
         <v>119</v>
       </c>
-      <c r="F11" s="31" t="s">
+      <c r="F11" s="41" t="s">
         <v>110</v>
       </c>
-      <c r="G11" s="31" t="s">
+      <c r="G11" s="41" t="s">
         <v>155</v>
       </c>
-      <c r="H11" s="33"/>
-    </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H11" s="42"/>
+    </row>
+    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B12" s="18">
         <v>10</v>
       </c>
-      <c r="C12" s="31" t="s">
+      <c r="C12" s="41" t="s">
         <v>120</v>
       </c>
-      <c r="D12" s="31"/>
-      <c r="E12" s="31" t="s">
+      <c r="D12" s="41"/>
+      <c r="E12" s="41" t="s">
         <v>121</v>
       </c>
-      <c r="F12" s="31" t="s">
+      <c r="F12" s="41" t="s">
         <v>110</v>
       </c>
-      <c r="G12" s="31" t="s">
+      <c r="G12" s="41" t="s">
         <v>155</v>
       </c>
-      <c r="H12" s="33"/>
-    </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H12" s="42"/>
+    </row>
+    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B13" s="18">
         <v>11</v>
       </c>
-      <c r="C13" s="31" t="s">
+      <c r="C13" s="41" t="s">
         <v>122</v>
       </c>
-      <c r="D13" s="31"/>
-      <c r="E13" s="31" t="s">
+      <c r="D13" s="41"/>
+      <c r="E13" s="41" t="s">
         <v>123</v>
       </c>
-      <c r="F13" s="31" t="s">
+      <c r="F13" s="41" t="s">
         <v>110</v>
       </c>
-      <c r="G13" s="31" t="s">
+      <c r="G13" s="41" t="s">
         <v>155</v>
       </c>
-      <c r="H13" s="33"/>
-    </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H13" s="42"/>
+    </row>
+    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B14" s="18">
         <v>12</v>
       </c>
-      <c r="C14" s="31" t="s">
+      <c r="C14" s="41" t="s">
         <v>124</v>
       </c>
-      <c r="D14" s="31"/>
-      <c r="E14" s="31" t="s">
+      <c r="D14" s="41"/>
+      <c r="E14" s="41" t="s">
         <v>125</v>
       </c>
-      <c r="F14" s="31" t="s">
+      <c r="F14" s="41" t="s">
         <v>110</v>
       </c>
-      <c r="G14" s="31" t="s">
+      <c r="G14" s="41" t="s">
         <v>155</v>
       </c>
-      <c r="H14" s="33"/>
-    </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H14" s="42"/>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="18">
         <v>13</v>
       </c>
-      <c r="C15" s="31" t="s">
+      <c r="C15" s="41" t="s">
         <v>126</v>
       </c>
-      <c r="D15" s="31"/>
-      <c r="E15" s="31" t="s">
+      <c r="D15" s="41"/>
+      <c r="E15" s="41" t="s">
         <v>127</v>
       </c>
-      <c r="F15" s="31" t="s">
+      <c r="F15" s="41" t="s">
         <v>110</v>
       </c>
-      <c r="G15" s="31" t="s">
+      <c r="G15" s="41" t="s">
         <v>155</v>
       </c>
-      <c r="H15" s="33"/>
-    </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H15" s="42"/>
+    </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" s="18">
         <v>14</v>
       </c>
-      <c r="C16" s="31" t="s">
+      <c r="C16" s="41" t="s">
         <v>128</v>
       </c>
-      <c r="D16" s="31"/>
-      <c r="E16" s="31" t="s">
+      <c r="D16" s="41"/>
+      <c r="E16" s="41" t="s">
         <v>129</v>
       </c>
-      <c r="F16" s="31" t="s">
+      <c r="F16" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="G16" s="31" t="s">
+      <c r="G16" s="41" t="s">
         <v>155</v>
       </c>
-      <c r="H16" s="33"/>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H16" s="42"/>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B17" s="18">
         <v>15</v>
       </c>
-      <c r="C17" s="31" t="s">
-        <v>102</v>
-      </c>
-      <c r="D17" s="31"/>
-      <c r="E17" s="31" t="s">
-        <v>103</v>
-      </c>
-      <c r="F17" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="G17" s="31" t="s">
+      <c r="C17" s="41" t="s">
+        <v>128</v>
+      </c>
+      <c r="D17" s="41"/>
+      <c r="E17" s="41" t="s">
+        <v>130</v>
+      </c>
+      <c r="F17" s="41" t="s">
+        <v>5</v>
+      </c>
+      <c r="G17" s="41" t="s">
         <v>156</v>
       </c>
-      <c r="H17" s="33"/>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H17" s="42"/>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="18">
         <v>16</v>
       </c>
-      <c r="C18" s="31" t="s">
-        <v>128</v>
-      </c>
-      <c r="D18" s="31"/>
-      <c r="E18" s="31" t="s">
-        <v>130</v>
-      </c>
-      <c r="F18" s="31" t="s">
-        <v>5</v>
-      </c>
-      <c r="G18" s="31" t="s">
+      <c r="C18" s="41" t="s">
+        <v>131</v>
+      </c>
+      <c r="D18" s="41"/>
+      <c r="E18" s="41" t="s">
+        <v>132</v>
+      </c>
+      <c r="F18" s="41" t="s">
+        <v>3</v>
+      </c>
+      <c r="G18" s="41" t="s">
         <v>156</v>
       </c>
-      <c r="H18" s="33"/>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H18" s="42"/>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="18">
         <v>17</v>
       </c>
-      <c r="C19" s="31" t="s">
-        <v>131</v>
-      </c>
-      <c r="D19" s="31"/>
-      <c r="E19" s="31" t="s">
-        <v>132</v>
-      </c>
-      <c r="F19" s="31" t="s">
-        <v>3</v>
-      </c>
-      <c r="G19" s="31" t="s">
+      <c r="C19" s="41" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19" s="41"/>
+      <c r="E19" s="41" t="s">
+        <v>133</v>
+      </c>
+      <c r="F19" s="41" t="s">
+        <v>6</v>
+      </c>
+      <c r="G19" s="41" t="s">
         <v>156</v>
       </c>
-      <c r="H19" s="33"/>
-    </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H19" s="42"/>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="18">
         <v>18</v>
       </c>
-      <c r="C20" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="D20" s="31"/>
-      <c r="E20" s="31" t="s">
-        <v>133</v>
-      </c>
-      <c r="F20" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="G20" s="31" t="s">
+      <c r="C20" s="41" t="s">
+        <v>134</v>
+      </c>
+      <c r="D20" s="41"/>
+      <c r="E20" s="41" t="s">
+        <v>135</v>
+      </c>
+      <c r="F20" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="G20" s="41" t="s">
         <v>156</v>
       </c>
-      <c r="H20" s="33"/>
-    </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H20" s="42"/>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="18">
         <v>19</v>
       </c>
-      <c r="C21" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="D21" s="31"/>
-      <c r="E21" s="31" t="s">
-        <v>135</v>
-      </c>
-      <c r="F21" s="31" t="s">
-        <v>4</v>
-      </c>
-      <c r="G21" s="31" t="s">
+      <c r="C21" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="D21" s="41"/>
+      <c r="E21" s="41" t="s">
+        <v>136</v>
+      </c>
+      <c r="F21" s="41" t="s">
+        <v>110</v>
+      </c>
+      <c r="G21" s="41" t="s">
         <v>156</v>
       </c>
-      <c r="H21" s="33"/>
-    </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H21" s="42"/>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="18">
         <v>20</v>
       </c>
-      <c r="C22" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="D22" s="31"/>
-      <c r="E22" s="31" t="s">
-        <v>136</v>
-      </c>
-      <c r="F22" s="31" t="s">
-        <v>110</v>
-      </c>
-      <c r="G22" s="31" t="s">
+      <c r="C22" s="41" t="s">
+        <v>137</v>
+      </c>
+      <c r="D22" s="41"/>
+      <c r="E22" s="41" t="s">
+        <v>138</v>
+      </c>
+      <c r="F22" s="41" t="s">
+        <v>6</v>
+      </c>
+      <c r="G22" s="41" t="s">
         <v>156</v>
       </c>
-      <c r="H22" s="33"/>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H22" s="42"/>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B23" s="18">
         <v>21</v>
       </c>
-      <c r="C23" s="31"/>
-      <c r="D23" s="31"/>
-      <c r="E23" s="31" t="s">
-        <v>107</v>
-      </c>
-      <c r="F23" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="G23" s="31" t="s">
+      <c r="C23" s="41" t="s">
+        <v>139</v>
+      </c>
+      <c r="D23" s="41"/>
+      <c r="E23" s="41" t="s">
+        <v>140</v>
+      </c>
+      <c r="F23" s="41" t="s">
+        <v>3</v>
+      </c>
+      <c r="G23" s="41" t="s">
         <v>156</v>
       </c>
-      <c r="H23" s="33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H23" s="42"/>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="18">
         <v>22</v>
       </c>
-      <c r="C24" s="31" t="s">
-        <v>137</v>
-      </c>
-      <c r="D24" s="31"/>
-      <c r="E24" s="31" t="s">
-        <v>138</v>
-      </c>
-      <c r="F24" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="G24" s="31" t="s">
+      <c r="C24" s="41" t="s">
+        <v>141</v>
+      </c>
+      <c r="D24" s="41"/>
+      <c r="E24" s="41" t="s">
+        <v>142</v>
+      </c>
+      <c r="F24" s="41" t="s">
+        <v>5</v>
+      </c>
+      <c r="G24" s="41" t="s">
         <v>156</v>
       </c>
-      <c r="H24" s="33"/>
-    </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H24" s="42"/>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B25" s="18">
         <v>23</v>
       </c>
-      <c r="C25" s="31" t="s">
-        <v>139</v>
-      </c>
-      <c r="D25" s="31"/>
-      <c r="E25" s="31" t="s">
-        <v>140</v>
-      </c>
-      <c r="F25" s="31" t="s">
+      <c r="C25" s="41" t="s">
+        <v>143</v>
+      </c>
+      <c r="D25" s="41"/>
+      <c r="E25" s="41" t="s">
+        <v>144</v>
+      </c>
+      <c r="F25" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="G25" s="31" t="s">
+      <c r="G25" s="41" t="s">
         <v>156</v>
       </c>
-      <c r="H25" s="33"/>
-    </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H25" s="42"/>
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="18">
         <v>24</v>
       </c>
-      <c r="C26" s="31" t="s">
-        <v>141</v>
-      </c>
-      <c r="D26" s="31"/>
-      <c r="E26" s="31" t="s">
-        <v>142</v>
-      </c>
-      <c r="F26" s="31" t="s">
+      <c r="C26" s="41" t="s">
+        <v>145</v>
+      </c>
+      <c r="D26" s="41"/>
+      <c r="E26" s="41" t="s">
+        <v>146</v>
+      </c>
+      <c r="F26" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="G26" s="31" t="s">
+      <c r="G26" s="41" t="s">
         <v>156</v>
       </c>
-      <c r="H26" s="33"/>
-    </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H26" s="42"/>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="18">
         <v>25</v>
       </c>
-      <c r="C27" s="31" t="s">
-        <v>143</v>
-      </c>
-      <c r="D27" s="31"/>
-      <c r="E27" s="31" t="s">
-        <v>144</v>
-      </c>
-      <c r="F27" s="31" t="s">
-        <v>3</v>
-      </c>
-      <c r="G27" s="31" t="s">
+      <c r="C27" s="41" t="s">
+        <v>147</v>
+      </c>
+      <c r="D27" s="41"/>
+      <c r="E27" s="41" t="s">
+        <v>148</v>
+      </c>
+      <c r="F27" s="41" t="s">
+        <v>149</v>
+      </c>
+      <c r="G27" s="41" t="s">
         <v>156</v>
       </c>
-      <c r="H27" s="33"/>
-    </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H27" s="42"/>
+    </row>
+    <row r="28" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B28" s="18">
         <v>26</v>
       </c>
-      <c r="C28" s="31" t="s">
-        <v>145</v>
-      </c>
-      <c r="D28" s="31"/>
-      <c r="E28" s="31" t="s">
-        <v>146</v>
-      </c>
-      <c r="F28" s="31" t="s">
-        <v>5</v>
-      </c>
-      <c r="G28" s="31" t="s">
-        <v>156</v>
-      </c>
-      <c r="H28" s="33"/>
-    </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B29" s="18">
-        <v>27</v>
-      </c>
-      <c r="C29" s="31" t="s">
-        <v>147</v>
-      </c>
-      <c r="D29" s="31"/>
-      <c r="E29" s="31" t="s">
-        <v>148</v>
-      </c>
-      <c r="F29" s="31" t="s">
+      <c r="C28" s="41" t="s">
+        <v>180</v>
+      </c>
+      <c r="D28" s="41"/>
+      <c r="E28" s="41" t="s">
+        <v>181</v>
+      </c>
+      <c r="F28" s="41" t="s">
         <v>149</v>
       </c>
-      <c r="G29" s="31" t="s">
-        <v>156</v>
-      </c>
-      <c r="H29" s="33"/>
+      <c r="G28" s="41" t="s">
+        <v>182</v>
+      </c>
+      <c r="H28" s="42"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="E1:E1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>

--- a/IA_CCBS_BANK_SIDE/RepaymentSchedule/RepaymentSchedule_Simulation.xlsx
+++ b/IA_CCBS_BANK_SIDE/RepaymentSchedule/RepaymentSchedule_Simulation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sw\Relational_Files\iApply\Interfaces\Interfaces_plus_allbanks\IA_CCBS_BANK_SIDE\RepaymentSchedule\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kmilos\source\repos\iApply_CCBS_API\IA_CCBS_BANK_SIDE\RepaymentSchedule\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D1CA37B-19AD-4739-8BAE-7EF9AFD6C251}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B64DB054-4842-40A8-9D0B-3DEE96D80FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-5550" windowWidth="30960" windowHeight="16920" xr2:uid="{CDB5EBE5-199B-4C02-A0AD-2F7510F763F7}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{CDB5EBE5-199B-4C02-A0AD-2F7510F763F7}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="3" r:id="rId1"/>
@@ -19,7 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Request!$C$2:$I$49</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Response!$C$2:$F$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Response!$C$2:$F$29</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="188">
   <si>
     <t>Description</t>
   </si>
@@ -581,15 +581,24 @@
     <t>dae</t>
   </si>
   <si>
-    <t>cr_laresc_save</t>
-  </si>
-  <si>
     <t>cr_laresc, 
 cr_laresc_insur_save</t>
   </si>
   <si>
     <t>cr_laresc,
 cr_laresc_insur_save</t>
+  </si>
+  <si>
+    <t>annualFee</t>
+  </si>
+  <si>
+    <t>cr_laresc_save.la_dae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cr_laresc_save.la_annual_fee </t>
+  </si>
+  <si>
+    <t>Annual Fee</t>
   </si>
 </sst>
 </file>
@@ -751,7 +760,7 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -881,6 +890,12 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1258,8 +1273,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{95AD6B62-2DA8-4727-83F6-7DF7747476EB}" name="Table4" displayName="Table4" ref="B2:H28" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
-  <autoFilter ref="B2:H28" xr:uid="{95AD6B62-2DA8-4727-83F6-7DF7747476EB}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{95AD6B62-2DA8-4727-83F6-7DF7747476EB}" name="Table4" displayName="Table4" ref="B2:H29" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
+  <autoFilter ref="B2:H29" xr:uid="{95AD6B62-2DA8-4727-83F6-7DF7747476EB}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:H27">
     <sortCondition ref="B2"/>
   </sortState>
@@ -1574,20 +1589,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{687BD6CA-6839-469E-8EB3-DB0965AE2362}">
   <dimension ref="B2:C15"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="17"/>
-    <col min="2" max="2" width="12.42578125" style="17" customWidth="1"/>
-    <col min="3" max="3" width="66.7109375" style="17" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="17"/>
+    <col min="1" max="1" width="9.109375" style="17"/>
+    <col min="2" max="2" width="12.44140625" style="17" customWidth="1"/>
+    <col min="3" max="3" width="66.6640625" style="17" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.109375" style="17"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C2" s="20" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B3" s="20" t="s">
         <v>9</v>
       </c>
@@ -1595,7 +1610,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B4" s="20" t="s">
         <v>11</v>
       </c>
@@ -1603,7 +1618,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B5" s="20" t="s">
         <v>17</v>
       </c>
@@ -1611,7 +1626,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B6" s="20" t="s">
         <v>19</v>
       </c>
@@ -1619,21 +1634,21 @@
         <v>179</v>
       </c>
     </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B7" s="20"/>
       <c r="C7" s="21"/>
     </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B8" s="20" t="s">
         <v>15</v>
       </c>
       <c r="C8" s="21"/>
     </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B9" s="20"/>
       <c r="C9" s="21"/>
     </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B10" s="20" t="s">
         <v>12</v>
       </c>
@@ -1641,7 +1656,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B11" s="20" t="s">
         <v>14</v>
       </c>
@@ -1649,15 +1664,15 @@
         <v>151</v>
       </c>
     </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B12" s="20"/>
       <c r="C12" s="21"/>
     </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B13" s="20"/>
       <c r="C13" s="21"/>
     </row>
-    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B14" s="20" t="s">
         <v>18</v>
       </c>
@@ -1665,7 +1680,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B15" s="20"/>
       <c r="C15" s="21"/>
     </row>
@@ -1677,21 +1692,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA02E32A-0574-49FB-89B5-FAB0617EBB92}">
   <dimension ref="B1:I103"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.85546875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="23"/>
+    <col min="1" max="1" width="2.88671875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" style="23"/>
     <col min="3" max="3" width="33" style="2" customWidth="1"/>
-    <col min="4" max="4" width="25.5703125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="22.7109375" style="2" customWidth="1"/>
-    <col min="6" max="7" width="28.5703125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="16.28515625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="61.7109375" style="16" customWidth="1"/>
-    <col min="10" max="16384" width="9.140625" style="2"/>
+    <col min="4" max="4" width="25.5546875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="22.6640625" style="2" customWidth="1"/>
+    <col min="6" max="7" width="28.5546875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="16.33203125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="61.6640625" style="16" customWidth="1"/>
+    <col min="10" max="16384" width="9.109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="2:9" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:9" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:9" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="24" t="s">
         <v>16</v>
       </c>
@@ -1717,7 +1732,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="25">
         <v>1</v>
       </c>
@@ -1737,7 +1752,7 @@
       <c r="H3" s="38"/>
       <c r="I3" s="31"/>
     </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B4" s="25">
         <v>2</v>
       </c>
@@ -1759,7 +1774,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B5" s="25">
         <v>3</v>
       </c>
@@ -1779,7 +1794,7 @@
       <c r="H5" s="38"/>
       <c r="I5" s="31"/>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B6" s="25">
         <v>4</v>
       </c>
@@ -1799,7 +1814,7 @@
       <c r="H6" s="38"/>
       <c r="I6" s="31"/>
     </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B7" s="25">
         <v>5</v>
       </c>
@@ -1819,7 +1834,7 @@
       <c r="H7" s="38"/>
       <c r="I7" s="33"/>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B8" s="25">
         <v>6</v>
       </c>
@@ -1839,7 +1854,7 @@
       <c r="H8" s="38"/>
       <c r="I8" s="33"/>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B9" s="25">
         <v>7</v>
       </c>
@@ -1859,7 +1874,7 @@
       <c r="H9" s="38"/>
       <c r="I9" s="33"/>
     </row>
-    <row r="10" spans="2:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B10" s="25">
         <v>8</v>
       </c>
@@ -1879,7 +1894,7 @@
       <c r="H10" s="38"/>
       <c r="I10" s="33"/>
     </row>
-    <row r="11" spans="2:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B11" s="25">
         <v>9</v>
       </c>
@@ -1899,7 +1914,7 @@
       <c r="H11" s="38"/>
       <c r="I11" s="33"/>
     </row>
-    <row r="12" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B12" s="25">
         <v>10</v>
       </c>
@@ -1919,7 +1934,7 @@
       <c r="H12" s="38"/>
       <c r="I12" s="33"/>
     </row>
-    <row r="13" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B13" s="25">
         <v>11</v>
       </c>
@@ -1939,7 +1954,7 @@
       <c r="H13" s="38"/>
       <c r="I13" s="33"/>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B14" s="25">
         <v>12</v>
       </c>
@@ -1959,7 +1974,7 @@
       <c r="H14" s="38"/>
       <c r="I14" s="33"/>
     </row>
-    <row r="15" spans="2:9" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:9" ht="27.6" x14ac:dyDescent="0.3">
       <c r="B15" s="25">
         <v>13</v>
       </c>
@@ -1981,7 +1996,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="16" spans="2:9" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:9" ht="27.6" x14ac:dyDescent="0.3">
       <c r="B16" s="25">
         <v>14</v>
       </c>
@@ -2005,7 +2020,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B17" s="25">
         <v>15</v>
       </c>
@@ -2025,7 +2040,7 @@
       <c r="H17" s="38"/>
       <c r="I17" s="33"/>
     </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B18" s="25">
         <v>16</v>
       </c>
@@ -2045,7 +2060,7 @@
       <c r="H18" s="38"/>
       <c r="I18" s="33"/>
     </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B19" s="25">
         <v>17</v>
       </c>
@@ -2065,7 +2080,7 @@
       <c r="H19" s="38"/>
       <c r="I19" s="33"/>
     </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B20" s="25">
         <v>18</v>
       </c>
@@ -2085,7 +2100,7 @@
       <c r="H20" s="38"/>
       <c r="I20" s="33"/>
     </row>
-    <row r="21" spans="2:9" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:9" ht="27.6" x14ac:dyDescent="0.3">
       <c r="B21" s="25">
         <v>19</v>
       </c>
@@ -2109,7 +2124,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B22" s="25">
         <v>20</v>
       </c>
@@ -2129,7 +2144,7 @@
       <c r="H22" s="38"/>
       <c r="I22" s="33"/>
     </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B23" s="25">
         <v>21</v>
       </c>
@@ -2151,7 +2166,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B24" s="25">
         <v>22</v>
       </c>
@@ -2171,7 +2186,7 @@
       <c r="H24" s="38"/>
       <c r="I24" s="33"/>
     </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B25" s="25">
         <v>23</v>
       </c>
@@ -2193,7 +2208,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="26" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B26" s="25">
         <v>24</v>
       </c>
@@ -2213,7 +2228,7 @@
       <c r="H26" s="38"/>
       <c r="I26" s="33"/>
     </row>
-    <row r="27" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B27" s="25">
         <v>25</v>
       </c>
@@ -2233,7 +2248,7 @@
       <c r="H27" s="38"/>
       <c r="I27" s="33"/>
     </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B28" s="25">
         <v>26</v>
       </c>
@@ -2253,7 +2268,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="2:9" s="3" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:9" s="3" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="B29" s="25">
         <v>27</v>
       </c>
@@ -2275,7 +2290,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="30" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B30" s="25">
         <v>28</v>
       </c>
@@ -2295,7 +2310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B31" s="25">
         <v>29</v>
       </c>
@@ -2315,7 +2330,7 @@
       <c r="H31" s="38"/>
       <c r="I31" s="33"/>
     </row>
-    <row r="32" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B32" s="25">
         <v>30</v>
       </c>
@@ -2335,7 +2350,7 @@
       <c r="H32" s="38"/>
       <c r="I32" s="33"/>
     </row>
-    <row r="33" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B33" s="25">
         <v>31</v>
       </c>
@@ -2355,7 +2370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B34" s="25">
         <v>32</v>
       </c>
@@ -2375,7 +2390,7 @@
       <c r="H34" s="38"/>
       <c r="I34" s="33"/>
     </row>
-    <row r="35" spans="2:9" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:9" ht="27.6" x14ac:dyDescent="0.3">
       <c r="B35" s="25">
         <v>33</v>
       </c>
@@ -2395,7 +2410,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="36" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B36" s="25">
         <v>34</v>
       </c>
@@ -2415,7 +2430,7 @@
       <c r="H36" s="38"/>
       <c r="I36" s="33"/>
     </row>
-    <row r="37" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B37" s="25">
         <v>35</v>
       </c>
@@ -2435,7 +2450,7 @@
       <c r="H37" s="38"/>
       <c r="I37" s="33"/>
     </row>
-    <row r="38" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B38" s="25">
         <v>36</v>
       </c>
@@ -2455,7 +2470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B39" s="25">
         <v>37</v>
       </c>
@@ -2475,7 +2490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B40" s="25">
         <v>38</v>
       </c>
@@ -2495,7 +2510,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B41" s="25">
         <v>39</v>
       </c>
@@ -2515,7 +2530,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B42" s="25">
         <v>40</v>
       </c>
@@ -2537,7 +2552,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="43" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B43" s="25">
         <v>41</v>
       </c>
@@ -2557,7 +2572,7 @@
       <c r="H43" s="38"/>
       <c r="I43" s="33"/>
     </row>
-    <row r="44" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B44" s="25">
         <v>42</v>
       </c>
@@ -2577,7 +2592,7 @@
       <c r="H44" s="38"/>
       <c r="I44" s="33"/>
     </row>
-    <row r="45" spans="2:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B45" s="25">
         <v>43</v>
       </c>
@@ -2597,7 +2612,7 @@
       </c>
       <c r="I45" s="35"/>
     </row>
-    <row r="46" spans="2:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B46" s="25">
         <v>44</v>
       </c>
@@ -2619,7 +2634,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="47" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B47" s="25">
         <v>45</v>
       </c>
@@ -2641,7 +2656,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="48" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B48" s="25">
         <v>46</v>
       </c>
@@ -2663,7 +2678,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="49" spans="2:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B49" s="25">
         <v>47</v>
       </c>
@@ -2685,7 +2700,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="50" spans="2:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B50" s="26"/>
       <c r="C50" s="7"/>
       <c r="D50" s="22"/>
@@ -2695,7 +2710,7 @@
       <c r="H50" s="8"/>
       <c r="I50" s="7"/>
     </row>
-    <row r="51" spans="2:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B51" s="26"/>
       <c r="C51" s="7"/>
       <c r="D51" s="22"/>
@@ -2705,7 +2720,7 @@
       <c r="H51" s="8"/>
       <c r="I51" s="7"/>
     </row>
-    <row r="52" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C52" s="9"/>
       <c r="D52" s="9"/>
       <c r="E52" s="9"/>
@@ -2714,7 +2729,7 @@
       <c r="H52" s="10"/>
       <c r="I52" s="9"/>
     </row>
-    <row r="53" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C53" s="5"/>
       <c r="D53" s="5"/>
       <c r="E53" s="5"/>
@@ -2723,7 +2738,7 @@
       <c r="H53" s="6"/>
       <c r="I53" s="5"/>
     </row>
-    <row r="54" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B54" s="27"/>
       <c r="C54" s="5"/>
       <c r="D54" s="5"/>
@@ -2733,7 +2748,7 @@
       <c r="H54" s="6"/>
       <c r="I54" s="5"/>
     </row>
-    <row r="55" spans="2:9" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:9" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B55" s="28"/>
       <c r="C55" s="9"/>
       <c r="D55" s="9"/>
@@ -2743,7 +2758,7 @@
       <c r="H55" s="10"/>
       <c r="I55" s="9"/>
     </row>
-    <row r="56" spans="2:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B56" s="26"/>
       <c r="C56" s="9"/>
       <c r="D56" s="9"/>
@@ -2753,7 +2768,7 @@
       <c r="H56" s="10"/>
       <c r="I56" s="9"/>
     </row>
-    <row r="57" spans="2:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B57" s="26"/>
       <c r="C57" s="9"/>
       <c r="D57" s="9"/>
@@ -2763,7 +2778,7 @@
       <c r="H57" s="10"/>
       <c r="I57" s="9"/>
     </row>
-    <row r="58" spans="2:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B58" s="26"/>
       <c r="C58" s="9"/>
       <c r="D58" s="9"/>
@@ -2773,7 +2788,7 @@
       <c r="H58" s="10"/>
       <c r="I58" s="9"/>
     </row>
-    <row r="59" spans="2:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B59" s="26"/>
       <c r="C59" s="12"/>
       <c r="D59" s="12"/>
@@ -2783,7 +2798,7 @@
       <c r="H59" s="13"/>
       <c r="I59" s="12"/>
     </row>
-    <row r="60" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C60" s="5"/>
       <c r="D60" s="5"/>
       <c r="E60" s="5"/>
@@ -2792,7 +2807,7 @@
       <c r="H60" s="6"/>
       <c r="I60" s="5"/>
     </row>
-    <row r="61" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C61" s="5"/>
       <c r="D61" s="5"/>
       <c r="E61" s="5"/>
@@ -2801,7 +2816,7 @@
       <c r="H61" s="6"/>
       <c r="I61" s="5"/>
     </row>
-    <row r="62" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C62" s="5"/>
       <c r="D62" s="5"/>
       <c r="E62" s="5"/>
@@ -2810,7 +2825,7 @@
       <c r="H62" s="6"/>
       <c r="I62" s="5"/>
     </row>
-    <row r="63" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C63" s="5"/>
       <c r="D63" s="5"/>
       <c r="E63" s="5"/>
@@ -2819,7 +2834,7 @@
       <c r="H63" s="6"/>
       <c r="I63" s="5"/>
     </row>
-    <row r="64" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B64" s="27"/>
       <c r="C64" s="5"/>
       <c r="D64" s="5"/>
@@ -2829,7 +2844,7 @@
       <c r="H64" s="6"/>
       <c r="I64" s="5"/>
     </row>
-    <row r="65" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B65" s="27"/>
       <c r="C65" s="9"/>
       <c r="D65" s="9"/>
@@ -2839,7 +2854,7 @@
       <c r="H65" s="10"/>
       <c r="I65" s="9"/>
     </row>
-    <row r="66" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B66" s="27"/>
       <c r="C66" s="9"/>
       <c r="D66" s="9"/>
@@ -2849,7 +2864,7 @@
       <c r="H66" s="10"/>
       <c r="I66" s="9"/>
     </row>
-    <row r="67" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C67" s="5"/>
       <c r="D67" s="5"/>
       <c r="E67" s="5"/>
@@ -2858,7 +2873,7 @@
       <c r="H67" s="6"/>
       <c r="I67" s="5"/>
     </row>
-    <row r="68" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C68" s="5"/>
       <c r="D68" s="5"/>
       <c r="E68" s="5"/>
@@ -2867,7 +2882,7 @@
       <c r="H68" s="6"/>
       <c r="I68" s="5"/>
     </row>
-    <row r="69" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C69" s="9"/>
       <c r="D69" s="9"/>
       <c r="E69" s="9"/>
@@ -2876,7 +2891,7 @@
       <c r="H69" s="10"/>
       <c r="I69" s="9"/>
     </row>
-    <row r="70" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C70" s="5"/>
       <c r="D70" s="5"/>
       <c r="E70" s="5"/>
@@ -2885,7 +2900,7 @@
       <c r="H70" s="6"/>
       <c r="I70" s="5"/>
     </row>
-    <row r="71" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C71" s="5"/>
       <c r="D71" s="5"/>
       <c r="E71" s="5"/>
@@ -2894,7 +2909,7 @@
       <c r="H71" s="6"/>
       <c r="I71" s="14"/>
     </row>
-    <row r="72" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C72" s="5"/>
       <c r="D72" s="5"/>
       <c r="E72" s="5"/>
@@ -2903,7 +2918,7 @@
       <c r="H72" s="6"/>
       <c r="I72" s="14"/>
     </row>
-    <row r="73" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C73" s="5"/>
       <c r="D73" s="5"/>
       <c r="E73" s="5"/>
@@ -2912,7 +2927,7 @@
       <c r="H73" s="6"/>
       <c r="I73" s="14"/>
     </row>
-    <row r="74" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B74" s="27"/>
       <c r="C74" s="5"/>
       <c r="D74" s="5"/>
@@ -2922,7 +2937,7 @@
       <c r="H74" s="6"/>
       <c r="I74" s="5"/>
     </row>
-    <row r="75" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B75" s="27"/>
       <c r="C75" s="5"/>
       <c r="D75" s="5"/>
@@ -2932,7 +2947,7 @@
       <c r="H75" s="6"/>
       <c r="I75" s="5"/>
     </row>
-    <row r="76" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B76" s="27"/>
       <c r="C76" s="5"/>
       <c r="D76" s="5"/>
@@ -2942,7 +2957,7 @@
       <c r="H76" s="6"/>
       <c r="I76" s="5"/>
     </row>
-    <row r="77" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C77" s="5"/>
       <c r="D77" s="5"/>
       <c r="E77" s="5"/>
@@ -2951,7 +2966,7 @@
       <c r="H77" s="6"/>
       <c r="I77" s="5"/>
     </row>
-    <row r="78" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C78" s="5"/>
       <c r="D78" s="5"/>
       <c r="E78" s="5"/>
@@ -2960,7 +2975,7 @@
       <c r="H78" s="6"/>
       <c r="I78" s="5"/>
     </row>
-    <row r="79" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C79" s="5"/>
       <c r="D79" s="5"/>
       <c r="E79" s="5"/>
@@ -2969,7 +2984,7 @@
       <c r="H79" s="6"/>
       <c r="I79" s="5"/>
     </row>
-    <row r="80" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C80" s="5"/>
       <c r="D80" s="5"/>
       <c r="E80" s="5"/>
@@ -2978,7 +2993,7 @@
       <c r="H80" s="6"/>
       <c r="I80" s="5"/>
     </row>
-    <row r="81" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C81" s="5"/>
       <c r="D81" s="5"/>
       <c r="E81" s="5"/>
@@ -2987,7 +3002,7 @@
       <c r="H81" s="6"/>
       <c r="I81" s="5"/>
     </row>
-    <row r="82" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C82" s="5"/>
       <c r="D82" s="5"/>
       <c r="E82" s="5"/>
@@ -2996,7 +3011,7 @@
       <c r="H82" s="6"/>
       <c r="I82" s="5"/>
     </row>
-    <row r="83" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C83" s="5"/>
       <c r="D83" s="5"/>
       <c r="E83" s="5"/>
@@ -3005,7 +3020,7 @@
       <c r="H83" s="6"/>
       <c r="I83" s="5"/>
     </row>
-    <row r="84" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C84" s="5"/>
       <c r="D84" s="5"/>
       <c r="E84" s="5"/>
@@ -3014,7 +3029,7 @@
       <c r="H84" s="6"/>
       <c r="I84" s="5"/>
     </row>
-    <row r="85" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C85" s="5"/>
       <c r="D85" s="5"/>
       <c r="E85" s="5"/>
@@ -3023,7 +3038,7 @@
       <c r="H85" s="6"/>
       <c r="I85" s="5"/>
     </row>
-    <row r="86" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C86" s="5"/>
       <c r="D86" s="5"/>
       <c r="E86" s="5"/>
@@ -3032,7 +3047,7 @@
       <c r="H86" s="6"/>
       <c r="I86" s="5"/>
     </row>
-    <row r="87" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C87" s="5"/>
       <c r="D87" s="5"/>
       <c r="E87" s="5"/>
@@ -3041,7 +3056,7 @@
       <c r="H87" s="6"/>
       <c r="I87" s="5"/>
     </row>
-    <row r="88" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C88" s="5"/>
       <c r="D88" s="5"/>
       <c r="E88" s="5"/>
@@ -3050,7 +3065,7 @@
       <c r="H88" s="6"/>
       <c r="I88" s="5"/>
     </row>
-    <row r="89" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C89" s="5"/>
       <c r="D89" s="5"/>
       <c r="E89" s="5"/>
@@ -3059,7 +3074,7 @@
       <c r="H89" s="6"/>
       <c r="I89" s="7"/>
     </row>
-    <row r="90" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C90" s="5"/>
       <c r="D90" s="5"/>
       <c r="E90" s="5"/>
@@ -3068,7 +3083,7 @@
       <c r="H90" s="6"/>
       <c r="I90" s="7"/>
     </row>
-    <row r="91" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C91" s="5"/>
       <c r="D91" s="5"/>
       <c r="E91" s="5"/>
@@ -3077,7 +3092,7 @@
       <c r="H91" s="6"/>
       <c r="I91" s="7"/>
     </row>
-    <row r="92" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C92" s="5"/>
       <c r="D92" s="5"/>
       <c r="E92" s="5"/>
@@ -3086,7 +3101,7 @@
       <c r="H92" s="6"/>
       <c r="I92" s="5"/>
     </row>
-    <row r="93" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C93" s="5"/>
       <c r="D93" s="5"/>
       <c r="E93" s="5"/>
@@ -3095,7 +3110,7 @@
       <c r="H93" s="6"/>
       <c r="I93" s="5"/>
     </row>
-    <row r="94" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C94" s="5"/>
       <c r="D94" s="5"/>
       <c r="E94" s="5"/>
@@ -3104,7 +3119,7 @@
       <c r="H94" s="6"/>
       <c r="I94" s="5"/>
     </row>
-    <row r="95" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C95" s="5"/>
       <c r="D95" s="5"/>
       <c r="E95" s="5"/>
@@ -3113,7 +3128,7 @@
       <c r="H95" s="6"/>
       <c r="I95" s="5"/>
     </row>
-    <row r="96" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C96" s="5"/>
       <c r="D96" s="5"/>
       <c r="E96" s="5"/>
@@ -3122,7 +3137,7 @@
       <c r="H96" s="6"/>
       <c r="I96" s="5"/>
     </row>
-    <row r="97" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B97" s="27"/>
       <c r="C97" s="9"/>
       <c r="D97" s="9"/>
@@ -3132,7 +3147,7 @@
       <c r="H97" s="10"/>
       <c r="I97" s="9"/>
     </row>
-    <row r="98" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B98" s="27"/>
       <c r="C98" s="5"/>
       <c r="D98" s="5"/>
@@ -3142,7 +3157,7 @@
       <c r="H98" s="6"/>
       <c r="I98" s="5"/>
     </row>
-    <row r="99" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:9" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B99" s="27"/>
       <c r="C99" s="5"/>
       <c r="D99" s="5"/>
@@ -3152,7 +3167,7 @@
       <c r="H99" s="6"/>
       <c r="I99" s="5"/>
     </row>
-    <row r="100" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C100" s="5"/>
       <c r="D100" s="5"/>
       <c r="E100" s="5"/>
@@ -3161,7 +3176,7 @@
       <c r="H100" s="6"/>
       <c r="I100" s="5"/>
     </row>
-    <row r="101" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C101" s="5"/>
       <c r="D101" s="5"/>
       <c r="E101" s="5"/>
@@ -3170,7 +3185,7 @@
       <c r="H101" s="6"/>
       <c r="I101" s="5"/>
     </row>
-    <row r="102" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B102" s="29"/>
       <c r="C102" s="5"/>
       <c r="D102" s="5"/>
@@ -3180,7 +3195,7 @@
       <c r="H102" s="6"/>
       <c r="I102" s="5"/>
     </row>
-    <row r="103" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C103" s="5"/>
       <c r="D103" s="5"/>
       <c r="E103" s="5"/>
@@ -3213,18 +3228,18 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF72A13E-C145-44E7-92A5-8C7F37AE7802}">
-  <dimension ref="B2:H28"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B2:H29"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="17"/>
-    <col min="3" max="3" width="39.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="32.5703125" customWidth="1"/>
-    <col min="5" max="6" width="33.28515625" customWidth="1"/>
-    <col min="7" max="7" width="28.5703125" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" style="17"/>
+    <col min="3" max="3" width="39.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="32.5546875" customWidth="1"/>
+    <col min="5" max="6" width="33.33203125" customWidth="1"/>
+    <col min="7" max="7" width="28.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="18" t="s">
         <v>16</v>
       </c>
@@ -3247,7 +3262,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="2:8" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:8" ht="27.6" x14ac:dyDescent="0.3">
       <c r="B3" s="18">
         <v>1</v>
       </c>
@@ -3262,11 +3277,11 @@
         <v>6</v>
       </c>
       <c r="G3" s="43" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H3" s="42"/>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B4" s="18">
         <v>2</v>
       </c>
@@ -3285,7 +3300,7 @@
       </c>
       <c r="H4" s="42"/>
     </row>
-    <row r="5" spans="2:8" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:8" ht="27.6" x14ac:dyDescent="0.3">
       <c r="B5" s="18">
         <v>3</v>
       </c>
@@ -3300,13 +3315,13 @@
         <v>6</v>
       </c>
       <c r="G5" s="43" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H5" s="42">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B6" s="18">
         <v>4</v>
       </c>
@@ -3325,7 +3340,7 @@
       </c>
       <c r="H6" s="42"/>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B7" s="18">
         <v>5</v>
       </c>
@@ -3344,7 +3359,7 @@
       </c>
       <c r="H7" s="42"/>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B8" s="18">
         <v>6</v>
       </c>
@@ -3363,7 +3378,7 @@
       </c>
       <c r="H8" s="42"/>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B9" s="18">
         <v>7</v>
       </c>
@@ -3382,7 +3397,7 @@
       </c>
       <c r="H9" s="42"/>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B10" s="18">
         <v>8</v>
       </c>
@@ -3401,7 +3416,7 @@
       </c>
       <c r="H10" s="42"/>
     </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B11" s="18">
         <v>9</v>
       </c>
@@ -3420,7 +3435,7 @@
       </c>
       <c r="H11" s="42"/>
     </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B12" s="18">
         <v>10</v>
       </c>
@@ -3439,7 +3454,7 @@
       </c>
       <c r="H12" s="42"/>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B13" s="18">
         <v>11</v>
       </c>
@@ -3458,7 +3473,7 @@
       </c>
       <c r="H13" s="42"/>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B14" s="18">
         <v>12</v>
       </c>
@@ -3477,7 +3492,7 @@
       </c>
       <c r="H14" s="42"/>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B15" s="18">
         <v>13</v>
       </c>
@@ -3496,7 +3511,7 @@
       </c>
       <c r="H15" s="42"/>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B16" s="18">
         <v>14</v>
       </c>
@@ -3515,7 +3530,7 @@
       </c>
       <c r="H16" s="42"/>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B17" s="18">
         <v>15</v>
       </c>
@@ -3534,7 +3549,7 @@
       </c>
       <c r="H17" s="42"/>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B18" s="18">
         <v>16</v>
       </c>
@@ -3553,7 +3568,7 @@
       </c>
       <c r="H18" s="42"/>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B19" s="18">
         <v>17</v>
       </c>
@@ -3572,7 +3587,7 @@
       </c>
       <c r="H19" s="42"/>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B20" s="18">
         <v>18</v>
       </c>
@@ -3591,7 +3606,7 @@
       </c>
       <c r="H20" s="42"/>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B21" s="18">
         <v>19</v>
       </c>
@@ -3610,7 +3625,7 @@
       </c>
       <c r="H21" s="42"/>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B22" s="18">
         <v>20</v>
       </c>
@@ -3629,7 +3644,7 @@
       </c>
       <c r="H22" s="42"/>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B23" s="18">
         <v>21</v>
       </c>
@@ -3648,7 +3663,7 @@
       </c>
       <c r="H23" s="42"/>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B24" s="18">
         <v>22</v>
       </c>
@@ -3667,7 +3682,7 @@
       </c>
       <c r="H24" s="42"/>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B25" s="18">
         <v>23</v>
       </c>
@@ -3686,7 +3701,7 @@
       </c>
       <c r="H25" s="42"/>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B26" s="18">
         <v>24</v>
       </c>
@@ -3705,7 +3720,7 @@
       </c>
       <c r="H26" s="42"/>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B27" s="18">
         <v>25</v>
       </c>
@@ -3724,7 +3739,7 @@
       </c>
       <c r="H27" s="42"/>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B28" s="18">
         <v>26</v>
       </c>
@@ -3739,9 +3754,28 @@
         <v>149</v>
       </c>
       <c r="G28" s="41" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="H28" s="42"/>
+    </row>
+    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B29" s="18">
+        <v>27</v>
+      </c>
+      <c r="C29" s="44" t="s">
+        <v>187</v>
+      </c>
+      <c r="D29" s="44"/>
+      <c r="E29" s="44" t="s">
+        <v>184</v>
+      </c>
+      <c r="F29" s="44" t="s">
+        <v>110</v>
+      </c>
+      <c r="G29" s="41" t="s">
+        <v>186</v>
+      </c>
+      <c r="H29" s="45"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="E1:E1048576">
